--- a/AAII_Financials/Quarterly/WKSP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WKSP_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/WKSP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WKSP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>WKSP</t>
   </si>
@@ -656,114 +656,121 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -771,14 +778,14 @@
         <v>500</v>
       </c>
       <c r="E8" s="3">
+        <v>800</v>
+      </c>
+      <c r="F8" s="3">
+        <v>500</v>
+      </c>
+      <c r="G8" s="3">
         <v>200</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
       <c r="H8" s="3">
         <v>0</v>
       </c>
@@ -792,64 +799,70 @@
         <v>0</v>
       </c>
       <c r="L8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>100</v>
+      </c>
+      <c r="O8" s="3">
         <v>200</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3">
-        <v>100</v>
-      </c>
       <c r="P8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3">
         <v>100</v>
       </c>
       <c r="R8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8" s="3">
+        <v>100</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
         <v>1900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>200</v>
       </c>
-      <c r="X8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>700</v>
+      </c>
+      <c r="F9" s="3">
         <v>400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>200</v>
       </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
       <c r="H9" s="3">
         <v>0</v>
       </c>
@@ -860,10 +873,10 @@
         <v>0</v>
       </c>
       <c r="K9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M9" s="3">
         <v>100</v>
@@ -881,42 +894,48 @@
         <v>100</v>
       </c>
       <c r="R9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9" s="3">
+        <v>100</v>
+      </c>
+      <c r="T9" s="3">
+        <v>0</v>
+      </c>
+      <c r="U9" s="3">
         <v>1700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>400</v>
       </c>
-      <c r="W9" s="3">
-        <v>100</v>
-      </c>
-      <c r="X9" s="3">
-        <v>100</v>
-      </c>
       <c r="Y9" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA9" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10" s="3">
         <v>0</v>
@@ -931,23 +950,23 @@
         <v>0</v>
       </c>
       <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
         <v>-100</v>
       </c>
-      <c r="L10" s="3">
-        <v>0</v>
-      </c>
-      <c r="M10" s="3">
-        <v>100</v>
-      </c>
       <c r="N10" s="3">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3">
+        <v>100</v>
+      </c>
+      <c r="P10" s="3">
         <v>-100</v>
       </c>
-      <c r="O10" s="3">
-        <v>0</v>
-      </c>
-      <c r="P10" s="3">
-        <v>0</v>
-      </c>
       <c r="Q10" s="3">
         <v>0</v>
       </c>
@@ -955,13 +974,13 @@
         <v>0</v>
       </c>
       <c r="S10" s="3">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3">
         <v>200</v>
-      </c>
-      <c r="T10" s="3">
-        <v>200</v>
-      </c>
-      <c r="U10" s="3">
-        <v>100</v>
       </c>
       <c r="V10" s="3">
         <v>200</v>
@@ -970,13 +989,19 @@
         <v>100</v>
       </c>
       <c r="X10" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z10" s="3">
         <v>-100</v>
       </c>
-      <c r="Y10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,8 +1027,10 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1073,8 +1100,14 @@
       <c r="Y12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,8 +1177,14 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1159,14 +1198,14 @@
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>-300</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
@@ -1183,40 +1222,46 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>-300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>-300</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3" t="s">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1286,8 +1331,14 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1361,164 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E17" s="3">
         <v>4400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
+        <v>4400</v>
+      </c>
+      <c r="G17" s="3">
         <v>3900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>3600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>3500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>3000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>3300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>2200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-3700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-3600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-3500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-3000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-3300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-2800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-3700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-2000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-1000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>300</v>
       </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3">
         <v>-100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,37 +1544,39 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
         <v>100</v>
       </c>
       <c r="F20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
         <v>200</v>
       </c>
       <c r="I20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1548,81 +1615,93 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-3300</v>
-      </c>
-      <c r="E21" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-3200</v>
       </c>
       <c r="G21" s="3">
         <v>-3300</v>
       </c>
       <c r="H21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="J21" s="3">
         <v>-2400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-3200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-2700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-3800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-1900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-1000</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-400</v>
       </c>
       <c r="Q21" s="3">
         <v>-100</v>
       </c>
       <c r="R21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="S21" s="3">
         <v>-100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U21" s="3">
         <v>-300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>300</v>
       </c>
-      <c r="U21" s="3">
-        <v>0</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
+        <v>0</v>
+      </c>
+      <c r="X21" s="3">
         <v>-100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1630,25 +1709,25 @@
         <v>100</v>
       </c>
       <c r="E22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G22" s="3">
         <v>200</v>
       </c>
       <c r="H22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I22" s="3">
         <v>200</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1657,10 +1736,10 @@
         <v>0</v>
       </c>
       <c r="N22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P22" s="3">
         <v>200</v>
@@ -1669,7 +1748,7 @@
         <v>100</v>
       </c>
       <c r="R22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S22" s="3">
         <v>100</v>
@@ -1678,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="U22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1692,79 +1771,91 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-3900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-3800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-3500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-3500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-2900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-3400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-3800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-2100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-1200</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-200</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-600</v>
       </c>
       <c r="Q23" s="3">
         <v>-200</v>
       </c>
       <c r="R23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="S23" s="3">
         <v>-200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U23" s="3">
         <v>-400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>300</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
         <v>-100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1834,8 +1925,14 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +2002,168 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-3900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-3800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-3500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-3500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-3400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-3800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-2100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-1200</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-600</v>
       </c>
       <c r="Q26" s="3">
         <v>-200</v>
       </c>
       <c r="R26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="S26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U26" s="3">
         <v>-400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>300</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
         <v>-100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-3900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-3800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-3500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-3500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-3400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-3800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-2100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-1200</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-600</v>
       </c>
       <c r="Q27" s="3">
         <v>-200</v>
       </c>
       <c r="R27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="S27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U27" s="3">
         <v>-400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>300</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
         <v>-100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2233,14 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2310,14 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2387,14 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,38 +2464,44 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
         <v>-100</v>
       </c>
       <c r="F32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
         <v>-200</v>
       </c>
       <c r="I32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2400,81 +2539,93 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-3900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-3800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-3500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-3500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-3400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-3800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-2100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-1200</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-600</v>
       </c>
       <c r="Q33" s="3">
         <v>-200</v>
       </c>
       <c r="R33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="S33" s="3">
         <v>-200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U33" s="3">
         <v>-400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>300</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
         <v>-100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2695,173 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-3900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-3800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-3500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-3500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-3400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-3800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-2100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-1200</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-600</v>
       </c>
       <c r="Q35" s="3">
         <v>-200</v>
       </c>
       <c r="R35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="S35" s="3">
         <v>-200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U35" s="3">
         <v>-400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>300</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
         <v>-100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2887,10 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,79 +2916,87 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F41" s="3">
         <v>3000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>5900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>10500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>14600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>16700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>19100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>25800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>28600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>29000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>12300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>9300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>500</v>
       </c>
-      <c r="Q41" s="3">
-        <v>0</v>
-      </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
       <c r="S41" s="3">
         <v>0</v>
       </c>
       <c r="T41" s="3">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3">
+        <v>0</v>
+      </c>
+      <c r="V41" s="3">
         <v>200</v>
       </c>
-      <c r="U41" s="3">
-        <v>100</v>
-      </c>
-      <c r="V41" s="3">
-        <v>0</v>
-      </c>
       <c r="W41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="3">
         <v>200</v>
       </c>
-      <c r="Y41" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2887,58 +3066,64 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="E43" s="3">
         <v>600</v>
       </c>
       <c r="F43" s="3">
+        <v>700</v>
+      </c>
+      <c r="G43" s="3">
+        <v>600</v>
+      </c>
+      <c r="H43" s="3">
         <v>400</v>
-      </c>
-      <c r="G43" s="3">
-        <v>300</v>
-      </c>
-      <c r="H43" s="3">
-        <v>300</v>
       </c>
       <c r="I43" s="3">
         <v>300</v>
       </c>
       <c r="J43" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="K43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L43" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M43" s="3">
         <v>200</v>
       </c>
       <c r="N43" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O43" s="3">
+        <v>200</v>
+      </c>
+      <c r="P43" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q43" s="3">
         <v>300</v>
-      </c>
-      <c r="P43" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>200</v>
       </c>
       <c r="R43" s="3">
         <v>200</v>
       </c>
       <c r="S43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T43" s="3">
         <v>200</v>
@@ -2947,63 +3132,69 @@
         <v>100</v>
       </c>
       <c r="V43" s="3">
+        <v>200</v>
+      </c>
+      <c r="W43" s="3">
+        <v>100</v>
+      </c>
+      <c r="X43" s="3">
         <v>400</v>
       </c>
-      <c r="W43" s="3">
-        <v>100</v>
-      </c>
-      <c r="X43" s="3">
-        <v>0</v>
-      </c>
       <c r="Y43" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E44" s="3">
         <v>3600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
+        <v>3600</v>
+      </c>
+      <c r="G44" s="3">
         <v>2900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>500</v>
       </c>
-      <c r="L44" s="3">
-        <v>100</v>
-      </c>
-      <c r="M44" s="3">
-        <v>100</v>
-      </c>
       <c r="N44" s="3">
         <v>100</v>
       </c>
       <c r="O44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P44" s="3">
         <v>100</v>
       </c>
       <c r="Q44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R44" s="3">
         <v>100</v>
@@ -3012,10 +3203,10 @@
         <v>100</v>
       </c>
       <c r="T44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U44" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="V44" s="3">
         <v>200</v>
@@ -3024,155 +3215,173 @@
         <v>300</v>
       </c>
       <c r="X44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y44" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F45" s="3">
         <v>700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>2200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>2000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>3700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>5100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>4100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>4700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>7400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
+        <v>100</v>
+      </c>
+      <c r="S45" s="3">
         <v>300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3">
-        <v>100</v>
-      </c>
-      <c r="T45" s="3">
-        <v>0</v>
-      </c>
       <c r="U45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V45" s="3">
         <v>0</v>
       </c>
       <c r="W45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z45" s="3">
         <v>400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F46" s="3">
         <v>7900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>10500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>14700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>18300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>22100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>25700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>30800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>34000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>36800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>13100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>9800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>700</v>
-      </c>
-      <c r="U46" s="3">
-        <v>500</v>
-      </c>
-      <c r="V46" s="3">
-        <v>500</v>
       </c>
       <c r="W46" s="3">
         <v>500</v>
       </c>
       <c r="X46" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y46" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z46" s="3">
         <v>700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3186,10 +3395,10 @@
         <v>100</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I47" s="3">
         <v>0</v>
@@ -3227,11 +3436,11 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V47" s="3" t="s">
-        <v>4</v>
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3">
+        <v>0</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>4</v>
@@ -3242,50 +3451,56 @@
       <c r="Y47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>15400</v>
+      </c>
+      <c r="F48" s="3">
         <v>15300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>15100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>14000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>13100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>12600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>11700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>200</v>
       </c>
-      <c r="O48" s="3">
-        <v>100</v>
-      </c>
-      <c r="P48" s="3">
-        <v>100</v>
-      </c>
       <c r="Q48" s="3">
         <v>100</v>
       </c>
@@ -3293,16 +3508,16 @@
         <v>100</v>
       </c>
       <c r="S48" s="3">
+        <v>100</v>
+      </c>
+      <c r="T48" s="3">
+        <v>100</v>
+      </c>
+      <c r="U48" s="3">
         <v>200</v>
       </c>
-      <c r="T48" s="3">
-        <v>100</v>
-      </c>
-      <c r="U48" s="3">
-        <v>0</v>
-      </c>
       <c r="V48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
@@ -3313,8 +3528,14 @@
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3331,29 +3552,29 @@
         <v>1300</v>
       </c>
       <c r="H49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J49" s="3">
         <v>1000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>300</v>
       </c>
-      <c r="N49" s="3">
-        <v>100</v>
-      </c>
-      <c r="O49" s="3">
-        <v>100</v>
-      </c>
       <c r="P49" s="3">
         <v>100</v>
       </c>
@@ -3367,10 +3588,10 @@
         <v>100</v>
       </c>
       <c r="T49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -3384,8 +3605,14 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3682,14 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,8 +3759,14 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3576,11 +3815,11 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>4</v>
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
+        <v>0</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>4</v>
@@ -3588,17 +3827,23 @@
       <c r="V52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
-      <c r="X52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="3" t="s">
+      <c r="W52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3913,91 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>26000</v>
+      </c>
+      <c r="F54" s="3">
         <v>24600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>27000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>30100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>32800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>35700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>38200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>34000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>36300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>38600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>14400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>10200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>800</v>
-      </c>
-      <c r="U54" s="3">
-        <v>600</v>
-      </c>
-      <c r="V54" s="3">
-        <v>600</v>
       </c>
       <c r="W54" s="3">
         <v>600</v>
       </c>
       <c r="X54" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y54" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z54" s="3">
         <v>700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +4023,10 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,79 +4052,87 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F57" s="3">
         <v>1900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1000</v>
-      </c>
-      <c r="P57" s="3">
-        <v>900</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>900</v>
       </c>
       <c r="R57" s="3">
         <v>900</v>
       </c>
       <c r="S57" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="T57" s="3">
         <v>900</v>
       </c>
       <c r="U57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V57" s="3">
+        <v>900</v>
+      </c>
+      <c r="W57" s="3">
         <v>600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3876,16 +4143,16 @@
         <v>5300</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="H58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>300</v>
@@ -3903,22 +4170,22 @@
         <v>300</v>
       </c>
       <c r="O58" s="3">
+        <v>300</v>
+      </c>
+      <c r="P58" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q58" s="3">
         <v>700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>400</v>
-      </c>
-      <c r="S58" s="3">
-        <v>300</v>
-      </c>
-      <c r="T58" s="3">
-        <v>300</v>
       </c>
       <c r="U58" s="3">
         <v>300</v>
@@ -3935,13 +4202,19 @@
       <c r="Y58" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E59" s="3">
         <v>400</v>
@@ -3959,126 +4232,138 @@
         <v>400</v>
       </c>
       <c r="J59" s="3">
+        <v>400</v>
+      </c>
+      <c r="K59" s="3">
+        <v>400</v>
+      </c>
+      <c r="L59" s="3">
         <v>200</v>
-      </c>
-      <c r="K59" s="3">
-        <v>300</v>
-      </c>
-      <c r="L59" s="3">
-        <v>300</v>
       </c>
       <c r="M59" s="3">
         <v>300</v>
       </c>
       <c r="N59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="P59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F60" s="3">
         <v>7600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4089,10 +4374,10 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>5300</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>5300</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>5300</v>
@@ -4101,10 +4386,10 @@
         <v>5300</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -4148,47 +4433,53 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>500</v>
+      </c>
+      <c r="E62" s="3">
         <v>600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
+        <v>600</v>
+      </c>
+      <c r="G62" s="3">
         <v>700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>400</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
@@ -4204,11 +4495,11 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>4</v>
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
+        <v>0</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>4</v>
@@ -4219,8 +4510,14 @@
       <c r="Y62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4587,14 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4664,14 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,79 +4741,91 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F66" s="3">
         <v>8200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>7600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>8500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>8600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>8800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>8800</v>
-      </c>
-      <c r="J66" s="3">
-        <v>2100</v>
-      </c>
-      <c r="K66" s="3">
-        <v>2100</v>
       </c>
       <c r="L66" s="3">
         <v>2100</v>
       </c>
       <c r="M66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="N66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="O66" s="3">
         <v>1900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4851,10 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4924,14 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +5001,14 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +5078,14 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,79 +5155,91 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-52000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-48300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-44700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-40700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-36900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-33400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-29900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-27000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-23700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-20800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-17100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-14900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-14100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-12900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-12000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-11000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-10800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-10200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-10500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-10500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-10400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5309,14 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5386,14 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5463,91 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>18200</v>
+      </c>
+      <c r="F76" s="3">
         <v>16400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>19400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>21600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>24100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>26900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>29400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>31900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>34200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>36500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>12500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>8800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>-300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>-300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>-200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>-500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5617,173 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-3900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-3800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-3500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-3500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-3400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-3800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-2100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-1200</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-600</v>
       </c>
       <c r="Q81" s="3">
         <v>-200</v>
       </c>
       <c r="R81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="S81" s="3">
         <v>-200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U81" s="3">
         <v>-400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>300</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
         <v>-100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,43 +5809,45 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>100</v>
+      </c>
+      <c r="F83" s="3">
         <v>600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
         <v>400</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>100</v>
-      </c>
       <c r="K83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L83" s="3">
         <v>100</v>
       </c>
       <c r="M83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
@@ -5485,8 +5882,14 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5959,14 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +6036,14 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +6113,14 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +6190,14 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,52 +6267,58 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-3100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-3000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-2000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-2000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-200</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>0</v>
       </c>
       <c r="R89" s="3">
         <v>-200</v>
@@ -5894,25 +6327,31 @@
         <v>0</v>
       </c>
       <c r="T89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
         <v>200</v>
       </c>
-      <c r="U89" s="3">
-        <v>100</v>
-      </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3">
+        <v>100</v>
+      </c>
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-100</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,67 +6377,69 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-8400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>4</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S91" s="3">
+      <c r="S91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-100</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>4</v>
@@ -6009,8 +6450,14 @@
       <c r="Y91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6527,14 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,50 +6604,56 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1500</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-900</v>
       </c>
       <c r="H94" s="3">
         <v>-1200</v>
       </c>
       <c r="I94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-8400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
@@ -6202,28 +6661,34 @@
         <v>0</v>
       </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3" t="s">
+      <c r="W94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V94" s="3" t="s">
+      <c r="X94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3" t="s">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6714,10 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6320,8 +6787,14 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6864,14 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6941,14 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,79 +7018,91 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>100</v>
+        <v>3200</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="F100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>5400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
-        <v>100</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
+        <v>100</v>
+      </c>
+      <c r="N100" s="3">
         <v>20200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>3600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>8800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>1000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>600</v>
       </c>
-      <c r="Q100" s="3">
-        <v>100</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
+        <v>100</v>
+      </c>
+      <c r="T100" s="3">
         <v>200</v>
       </c>
-      <c r="S100" s="3">
-        <v>100</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
       <c r="W100" s="3">
-        <v>100</v>
-      </c>
-      <c r="X100" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y100" s="3" t="s">
+      <c r="AA100" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6651,15 +7148,15 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3" t="s">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
@@ -6667,64 +7164,70 @@
         <v>0</v>
       </c>
       <c r="W101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
       </c>
       <c r="Y101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>400</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-4600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-4100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-2700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-2500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-6100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-2800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-2400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>18700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>3000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>8200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>400</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
         <v>0</v>
       </c>
@@ -6732,18 +7235,24 @@
         <v>0</v>
       </c>
       <c r="U102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V102" s="3">
         <v>0</v>
       </c>
       <c r="W102" s="3">
+        <v>100</v>
+      </c>
+      <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-100</v>
       </c>
-      <c r="X102" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WKSP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WKSP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>WKSP</t>
   </si>
@@ -656,139 +656,143 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E8" s="3">
         <v>500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>200</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
       <c r="I8" s="3">
         <v>0</v>
       </c>
@@ -805,16 +809,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3">
+        <v>100</v>
+      </c>
+      <c r="P8" s="3">
         <v>200</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
       <c r="Q8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3">
         <v>100</v>
@@ -823,49 +827,52 @@
         <v>100</v>
       </c>
       <c r="T8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
         <v>1900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>200</v>
       </c>
-      <c r="Z8" s="3">
-        <v>0</v>
-      </c>
       <c r="AA8" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E9" s="3">
         <v>500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>200</v>
       </c>
-      <c r="H9" s="3">
-        <v>0</v>
-      </c>
       <c r="I9" s="3">
         <v>0</v>
       </c>
@@ -879,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N9" s="3">
         <v>100</v>
@@ -900,22 +907,22 @@
         <v>100</v>
       </c>
       <c r="T9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U9" s="3">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3">
         <v>1700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>700</v>
-      </c>
-      <c r="W9" s="3">
-        <v>400</v>
       </c>
       <c r="X9" s="3">
         <v>400</v>
       </c>
       <c r="Y9" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="Z9" s="3">
         <v>100</v>
@@ -923,22 +930,25 @@
       <c r="AA9" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3">
         <v>100</v>
       </c>
       <c r="G10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10" s="3">
         <v>0</v>
@@ -956,20 +966,20 @@
         <v>0</v>
       </c>
       <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
         <v>-100</v>
       </c>
-      <c r="N10" s="3">
-        <v>0</v>
-      </c>
       <c r="O10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P10" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="3">
         <v>-100</v>
       </c>
-      <c r="Q10" s="3">
-        <v>0</v>
-      </c>
       <c r="R10" s="3">
         <v>0</v>
       </c>
@@ -980,28 +990,31 @@
         <v>0</v>
       </c>
       <c r="U10" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V10" s="3">
         <v>200</v>
       </c>
       <c r="W10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X10" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y10" s="3">
         <v>200</v>
       </c>
-      <c r="Y10" s="3">
-        <v>100</v>
-      </c>
       <c r="Z10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA10" s="3">
         <v>-100</v>
       </c>
-      <c r="AA10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1029,8 +1042,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1106,8 +1120,11 @@
       <c r="AA12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,8 +1200,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1204,11 +1224,11 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-300</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
@@ -1228,25 +1248,25 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-200</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="3">
-        <v>-300</v>
+      <c r="U14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V14" s="3">
         <v>-300</v>
       </c>
       <c r="W14" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1257,11 +1277,14 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-      <c r="AA14" s="3" t="s">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1337,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E17" s="3">
         <v>4200</v>
-      </c>
-      <c r="E17" s="3">
-        <v>4400</v>
       </c>
       <c r="F17" s="3">
         <v>4400</v>
       </c>
       <c r="G17" s="3">
+        <v>4400</v>
+      </c>
+      <c r="H17" s="3">
         <v>3900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2100</v>
-      </c>
-      <c r="O17" s="3">
-        <v>1000</v>
       </c>
       <c r="P17" s="3">
         <v>1000</v>
       </c>
       <c r="Q17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R17" s="3">
         <v>300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>500</v>
-      </c>
-      <c r="S17" s="3">
-        <v>200</v>
       </c>
       <c r="T17" s="3">
         <v>200</v>
       </c>
       <c r="U17" s="3">
+        <v>200</v>
+      </c>
+      <c r="V17" s="3">
         <v>2200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>300</v>
       </c>
-      <c r="W18" s="3">
-        <v>0</v>
-      </c>
       <c r="X18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-400</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-300</v>
       </c>
       <c r="AA18" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,8 +1579,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1558,13 +1592,13 @@
         <v>100</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3">
         <v>200</v>
@@ -1573,13 +1607,13 @@
         <v>200</v>
       </c>
       <c r="K20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1621,87 +1655,93 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3400</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-3300</v>
       </c>
       <c r="G21" s="3">
         <v>-3300</v>
       </c>
       <c r="H21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="I21" s="3">
         <v>-3200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-3300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-3200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-400</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-100</v>
       </c>
       <c r="T21" s="3">
         <v>-100</v>
       </c>
       <c r="U21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V21" s="3">
         <v>-300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>300</v>
       </c>
-      <c r="W21" s="3">
-        <v>0</v>
-      </c>
       <c r="X21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-500</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>-300</v>
       </c>
       <c r="AA21" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1715,7 +1755,7 @@
         <v>100</v>
       </c>
       <c r="G22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H22" s="3">
         <v>200</v>
@@ -1724,14 +1764,14 @@
         <v>200</v>
       </c>
       <c r="J22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K22" s="3">
+        <v>100</v>
+      </c>
+      <c r="L22" s="3">
         <v>200</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1742,25 +1782,25 @@
         <v>0</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>200</v>
       </c>
-      <c r="Q22" s="3">
-        <v>100</v>
-      </c>
       <c r="R22" s="3">
+        <v>100</v>
+      </c>
+      <c r="S22" s="3">
         <v>200</v>
       </c>
-      <c r="S22" s="3">
-        <v>100</v>
-      </c>
       <c r="T22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -1777,85 +1817,91 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-3700</v>
+        <v>-4000</v>
       </c>
       <c r="E23" s="3">
         <v>-3700</v>
       </c>
       <c r="F23" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="G23" s="3">
         <v>-3900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3800</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-3500</v>
       </c>
       <c r="I23" s="3">
         <v>-3500</v>
       </c>
       <c r="J23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="K23" s="3">
         <v>-2900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-600</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-200</v>
       </c>
       <c r="T23" s="3">
         <v>-200</v>
       </c>
       <c r="U23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V23" s="3">
         <v>-400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>300</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
       <c r="X23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-500</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-300</v>
       </c>
       <c r="AA23" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1931,8 +1977,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-3700</v>
+        <v>-4000</v>
       </c>
       <c r="E26" s="3">
         <v>-3700</v>
       </c>
       <c r="F26" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="G26" s="3">
         <v>-3900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3800</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-3500</v>
       </c>
       <c r="I26" s="3">
         <v>-3500</v>
       </c>
       <c r="J26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="K26" s="3">
         <v>-2900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-600</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-200</v>
       </c>
       <c r="T26" s="3">
         <v>-200</v>
       </c>
       <c r="U26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V26" s="3">
         <v>-400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>300</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
       <c r="X26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-500</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-300</v>
       </c>
       <c r="AA26" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-3700</v>
+        <v>-4000</v>
       </c>
       <c r="E27" s="3">
         <v>-3700</v>
       </c>
       <c r="F27" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="G27" s="3">
         <v>-3900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3800</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-3500</v>
       </c>
       <c r="I27" s="3">
         <v>-3500</v>
       </c>
       <c r="J27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="K27" s="3">
         <v>-2900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-600</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-200</v>
       </c>
       <c r="T27" s="3">
         <v>-200</v>
       </c>
       <c r="U27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V27" s="3">
         <v>-400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>300</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
       <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-500</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>-300</v>
       </c>
       <c r="AA27" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2316,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,8 +2537,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2482,13 +2552,13 @@
         <v>-100</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-200</v>
       </c>
       <c r="I32" s="3">
         <v>-200</v>
@@ -2497,13 +2567,13 @@
         <v>-200</v>
       </c>
       <c r="K32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -2545,87 +2615,93 @@
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-3700</v>
+        <v>-4000</v>
       </c>
       <c r="E33" s="3">
         <v>-3700</v>
       </c>
       <c r="F33" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="G33" s="3">
         <v>-3900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3800</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-3500</v>
       </c>
       <c r="I33" s="3">
         <v>-3500</v>
       </c>
       <c r="J33" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="K33" s="3">
         <v>-2900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-600</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-200</v>
       </c>
       <c r="T33" s="3">
         <v>-200</v>
       </c>
       <c r="U33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V33" s="3">
         <v>-400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>300</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
       <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-500</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>-300</v>
       </c>
       <c r="AA33" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-3700</v>
+        <v>-4000</v>
       </c>
       <c r="E35" s="3">
         <v>-3700</v>
       </c>
       <c r="F35" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="G35" s="3">
         <v>-3900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3800</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-3500</v>
       </c>
       <c r="I35" s="3">
         <v>-3500</v>
       </c>
       <c r="J35" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="K35" s="3">
         <v>-2900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-600</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-200</v>
       </c>
       <c r="T35" s="3">
         <v>-200</v>
       </c>
       <c r="U35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V35" s="3">
         <v>-400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>300</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
       <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-500</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>-300</v>
       </c>
       <c r="AA35" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,59 +3004,60 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E41" s="3">
         <v>3500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>16700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>19100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>25800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>28600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>29000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>12300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>500</v>
       </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
       <c r="T41" s="3">
         <v>0</v>
       </c>
@@ -2978,25 +3065,28 @@
         <v>0</v>
       </c>
       <c r="V41" s="3">
+        <v>0</v>
+      </c>
+      <c r="W41" s="3">
         <v>200</v>
       </c>
-      <c r="W41" s="3">
-        <v>100</v>
-      </c>
       <c r="X41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y41" s="3">
         <v>0</v>
       </c>
       <c r="Z41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="3">
         <v>200</v>
       </c>
-      <c r="AA41" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3072,28 +3162,31 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>800</v>
+      </c>
+      <c r="E43" s="3">
         <v>300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>400</v>
-      </c>
-      <c r="I43" s="3">
-        <v>300</v>
       </c>
       <c r="J43" s="3">
         <v>300</v>
@@ -3102,25 +3195,25 @@
         <v>300</v>
       </c>
       <c r="L43" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="M43" s="3">
+        <v>100</v>
+      </c>
+      <c r="N43" s="3">
         <v>200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>200</v>
       </c>
-      <c r="P43" s="3">
-        <v>100</v>
-      </c>
       <c r="Q43" s="3">
+        <v>100</v>
+      </c>
+      <c r="R43" s="3">
         <v>300</v>
-      </c>
-      <c r="R43" s="3">
-        <v>200</v>
       </c>
       <c r="S43" s="3">
         <v>200</v>
@@ -3129,64 +3222,67 @@
         <v>200</v>
       </c>
       <c r="U43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V43" s="3">
+        <v>100</v>
+      </c>
+      <c r="W43" s="3">
         <v>200</v>
       </c>
-      <c r="W43" s="3">
-        <v>100</v>
-      </c>
       <c r="X43" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y43" s="3">
         <v>400</v>
       </c>
-      <c r="Y43" s="3">
-        <v>100</v>
-      </c>
       <c r="Z43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA43" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E44" s="3">
         <v>6500</v>
-      </c>
-      <c r="E44" s="3">
-        <v>3600</v>
       </c>
       <c r="F44" s="3">
         <v>3600</v>
       </c>
       <c r="G44" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H44" s="3">
         <v>2900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1600</v>
-      </c>
-      <c r="I44" s="3">
-        <v>1300</v>
       </c>
       <c r="J44" s="3">
         <v>1300</v>
       </c>
       <c r="K44" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L44" s="3">
         <v>1100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>500</v>
       </c>
-      <c r="N44" s="3">
-        <v>100</v>
-      </c>
       <c r="O44" s="3">
         <v>100</v>
       </c>
@@ -3194,10 +3290,10 @@
         <v>100</v>
       </c>
       <c r="Q44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S44" s="3">
         <v>100</v>
@@ -3209,84 +3305,87 @@
         <v>100</v>
       </c>
       <c r="V44" s="3">
+        <v>100</v>
+      </c>
+      <c r="W44" s="3">
         <v>200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>300</v>
       </c>
-      <c r="Z44" s="3">
-        <v>100</v>
-      </c>
       <c r="AA44" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>200</v>
+      </c>
+      <c r="E45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3">
-        <v>100</v>
-      </c>
       <c r="S45" s="3">
+        <v>100</v>
+      </c>
+      <c r="T45" s="3">
         <v>300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3">
-        <v>100</v>
-      </c>
       <c r="V45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
@@ -3295,16 +3394,19 @@
         <v>0</v>
       </c>
       <c r="Y45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA45" s="3">
         <v>400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3312,61 +3414,61 @@
         <v>10700</v>
       </c>
       <c r="E46" s="3">
+        <v>10700</v>
+      </c>
+      <c r="F46" s="3">
         <v>9100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>22100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>30800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>34000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>36800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>900</v>
-      </c>
-      <c r="S46" s="3">
-        <v>500</v>
       </c>
       <c r="T46" s="3">
         <v>500</v>
       </c>
       <c r="U46" s="3">
+        <v>500</v>
+      </c>
+      <c r="V46" s="3">
         <v>300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>700</v>
-      </c>
-      <c r="W46" s="3">
-        <v>500</v>
       </c>
       <c r="X46" s="3">
         <v>500</v>
@@ -3375,13 +3477,16 @@
         <v>500</v>
       </c>
       <c r="Z46" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA46" s="3">
         <v>700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3401,7 +3506,7 @@
         <v>100</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J47" s="3">
         <v>0</v>
@@ -3442,8 +3547,8 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>4</v>
+      <c r="W47" s="3">
+        <v>0</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>4</v>
@@ -3457,53 +3562,56 @@
       <c r="AA47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E48" s="3">
         <v>15100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>15100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>11700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>200</v>
       </c>
-      <c r="Q48" s="3">
-        <v>100</v>
-      </c>
       <c r="R48" s="3">
         <v>100</v>
       </c>
@@ -3514,13 +3622,13 @@
         <v>100</v>
       </c>
       <c r="U48" s="3">
+        <v>100</v>
+      </c>
+      <c r="V48" s="3">
         <v>200</v>
       </c>
-      <c r="V48" s="3">
-        <v>100</v>
-      </c>
       <c r="W48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X48" s="3">
         <v>0</v>
@@ -3534,8 +3642,11 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3558,26 +3669,26 @@
         <v>1300</v>
       </c>
       <c r="J49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K49" s="3">
         <v>1000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>300</v>
       </c>
-      <c r="P49" s="3">
-        <v>100</v>
-      </c>
       <c r="Q49" s="3">
         <v>100</v>
       </c>
@@ -3594,7 +3705,7 @@
         <v>100</v>
       </c>
       <c r="V49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -3611,8 +3722,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,8 +3882,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3821,8 +3941,8 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>4</v>
+      <c r="U52" s="3">
+        <v>0</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>4</v>
@@ -3833,17 +3953,20 @@
       <c r="X52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
+      <c r="Y52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-      <c r="AA52" s="3" t="s">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,70 +4042,73 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E54" s="3">
         <v>27300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>26000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>24600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>30100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>32800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>35700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>38200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>34000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>36300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>38600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1100</v>
-      </c>
-      <c r="S54" s="3">
-        <v>700</v>
       </c>
       <c r="T54" s="3">
         <v>700</v>
       </c>
       <c r="U54" s="3">
+        <v>700</v>
+      </c>
+      <c r="V54" s="3">
         <v>500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>800</v>
-      </c>
-      <c r="W54" s="3">
-        <v>600</v>
       </c>
       <c r="X54" s="3">
         <v>600</v>
@@ -3991,13 +4117,16 @@
         <v>600</v>
       </c>
       <c r="Z54" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA54" s="3">
         <v>700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,55 +4184,56 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E57" s="3">
         <v>2300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
-      </c>
-      <c r="H57" s="3">
-        <v>2000</v>
       </c>
       <c r="I57" s="3">
         <v>2000</v>
       </c>
       <c r="J57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K57" s="3">
         <v>1800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>900</v>
-      </c>
-      <c r="P57" s="3">
-        <v>1000</v>
       </c>
       <c r="Q57" s="3">
         <v>1000</v>
       </c>
       <c r="R57" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="S57" s="3">
         <v>900</v>
@@ -4111,33 +4242,36 @@
         <v>900</v>
       </c>
       <c r="U57" s="3">
+        <v>900</v>
+      </c>
+      <c r="V57" s="3">
         <v>1000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>900</v>
-      </c>
-      <c r="W57" s="3">
-        <v>600</v>
       </c>
       <c r="X57" s="3">
         <v>600</v>
       </c>
       <c r="Y57" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z57" s="3">
         <v>400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5300</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
         <v>5300</v>
@@ -4149,13 +4283,13 @@
         <v>5300</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>300</v>
@@ -4176,19 +4310,19 @@
         <v>300</v>
       </c>
       <c r="Q58" s="3">
+        <v>300</v>
+      </c>
+      <c r="R58" s="3">
         <v>700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>400</v>
-      </c>
-      <c r="U58" s="3">
-        <v>300</v>
       </c>
       <c r="V58" s="3">
         <v>300</v>
@@ -4208,16 +4342,19 @@
       <c r="AA58" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>500</v>
+      </c>
+      <c r="E59" s="3">
         <v>300</v>
-      </c>
-      <c r="E59" s="3">
-        <v>400</v>
       </c>
       <c r="F59" s="3">
         <v>400</v>
@@ -4238,10 +4375,10 @@
         <v>400</v>
       </c>
       <c r="L59" s="3">
+        <v>400</v>
+      </c>
+      <c r="M59" s="3">
         <v>200</v>
-      </c>
-      <c r="M59" s="3">
-        <v>300</v>
       </c>
       <c r="N59" s="3">
         <v>300</v>
@@ -4250,125 +4387,131 @@
         <v>300</v>
       </c>
       <c r="P59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Q59" s="3">
         <v>100</v>
       </c>
       <c r="R59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S59" s="3">
         <v>0</v>
       </c>
       <c r="T59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U59" s="3">
         <v>100</v>
       </c>
       <c r="V59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W59" s="3">
         <v>0</v>
       </c>
       <c r="X59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y59" s="3">
         <v>100</v>
       </c>
       <c r="Z59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E60" s="3">
         <v>7800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2400</v>
-      </c>
-      <c r="I60" s="3">
-        <v>2500</v>
       </c>
       <c r="J60" s="3">
         <v>2500</v>
       </c>
       <c r="K60" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L60" s="3">
         <v>2400</v>
-      </c>
-      <c r="L60" s="3">
-        <v>1800</v>
       </c>
       <c r="M60" s="3">
         <v>1800</v>
       </c>
       <c r="N60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O60" s="3">
         <v>1700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1200</v>
-      </c>
-      <c r="W60" s="3">
-        <v>900</v>
       </c>
       <c r="X60" s="3">
         <v>900</v>
       </c>
       <c r="Y60" s="3">
+        <v>900</v>
+      </c>
+      <c r="Z60" s="3">
         <v>800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -4380,7 +4523,7 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>5300</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
         <v>5300</v>
@@ -4392,7 +4535,7 @@
         <v>5300</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -4439,8 +4582,11 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4448,40 +4594,40 @@
         <v>500</v>
       </c>
       <c r="E62" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F62" s="3">
         <v>600</v>
       </c>
       <c r="G62" s="3">
+        <v>600</v>
+      </c>
+      <c r="H62" s="3">
         <v>700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1100</v>
-      </c>
-      <c r="L62" s="3">
-        <v>300</v>
       </c>
       <c r="M62" s="3">
         <v>300</v>
       </c>
       <c r="N62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="O62" s="3">
         <v>400</v>
       </c>
       <c r="P62" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
@@ -4501,8 +4647,8 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>4</v>
+      <c r="W62" s="3">
+        <v>0</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>4</v>
@@ -4516,8 +4662,11 @@
       <c r="AA62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,37 +4902,40 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E66" s="3">
         <v>8400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8600</v>
-      </c>
-      <c r="J66" s="3">
-        <v>8800</v>
       </c>
       <c r="K66" s="3">
         <v>8800</v>
       </c>
       <c r="L66" s="3">
-        <v>2100</v>
+        <v>8800</v>
       </c>
       <c r="M66" s="3">
         <v>2100</v>
@@ -4786,46 +4944,49 @@
         <v>2100</v>
       </c>
       <c r="O66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="P66" s="3">
         <v>1900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1500</v>
-      </c>
-      <c r="T66" s="3">
-        <v>1400</v>
       </c>
       <c r="U66" s="3">
         <v>1400</v>
       </c>
       <c r="V66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W66" s="3">
         <v>1300</v>
-      </c>
-      <c r="W66" s="3">
-        <v>900</v>
       </c>
       <c r="X66" s="3">
         <v>900</v>
       </c>
       <c r="Y66" s="3">
+        <v>900</v>
+      </c>
+      <c r="Z66" s="3">
         <v>800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,85 +5332,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-52000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-48300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-44700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-40700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-36900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-33400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-29900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-27000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-23700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-20800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-17100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-14900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-12900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-12600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-12000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-11000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-10800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-10200</v>
-      </c>
-      <c r="W72" s="3">
-        <v>-10500</v>
       </c>
       <c r="X72" s="3">
         <v>-10500</v>
       </c>
       <c r="Y72" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="Z72" s="3">
         <v>-10400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-9900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,85 +5652,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E76" s="3">
         <v>18900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>19400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>21600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>24100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>26900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>29400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>31900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>34200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>36500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-400</v>
-      </c>
-      <c r="W76" s="3">
-        <v>-300</v>
       </c>
       <c r="X76" s="3">
         <v>-300</v>
       </c>
       <c r="Y76" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Z76" s="3">
         <v>-200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-3700</v>
+        <v>-4000</v>
       </c>
       <c r="E81" s="3">
         <v>-3700</v>
       </c>
       <c r="F81" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="G81" s="3">
         <v>-3900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3800</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-3500</v>
       </c>
       <c r="I81" s="3">
         <v>-3500</v>
       </c>
       <c r="J81" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="K81" s="3">
         <v>-2900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-600</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-200</v>
       </c>
       <c r="T81" s="3">
         <v>-200</v>
       </c>
       <c r="U81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V81" s="3">
         <v>-400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>300</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
       <c r="X81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-500</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>-300</v>
       </c>
       <c r="AA81" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,37 +6009,38 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>200</v>
+      </c>
+      <c r="E83" s="3">
         <v>400</v>
       </c>
-      <c r="E83" s="3">
-        <v>100</v>
-      </c>
       <c r="F83" s="3">
+        <v>100</v>
+      </c>
+      <c r="G83" s="3">
         <v>600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
       <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
         <v>400</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M83" s="3">
         <v>100</v>
@@ -5850,7 +6049,7 @@
         <v>100</v>
       </c>
       <c r="O83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -5888,8 +6087,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,85 +6487,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3000</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-2000</v>
       </c>
       <c r="M89" s="3">
         <v>-2000</v>
       </c>
       <c r="N89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="O89" s="3">
         <v>-1000</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-500</v>
       </c>
       <c r="P89" s="3">
         <v>-500</v>
       </c>
       <c r="Q89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R89" s="3">
         <v>-300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-200</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
         <v>-200</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
         <v>200</v>
       </c>
-      <c r="W89" s="3">
-        <v>100</v>
-      </c>
       <c r="X89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-100</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,55 +6599,56 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>-200</v>
       </c>
       <c r="F91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>4</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>4</v>
@@ -6435,14 +6656,14 @@
       <c r="T91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U91" s="3">
-        <v>-100</v>
+      <c r="U91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
+      <c r="W91" s="3">
+        <v>-100</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>4</v>
@@ -6456,8 +6677,11 @@
       <c r="AA91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,53 +6837,56 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
         <v>-200</v>
       </c>
       <c r="F94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G94" s="3">
         <v>-800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
@@ -6667,28 +6897,31 @@
         <v>0</v>
       </c>
       <c r="U94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>4</v>
+      <c r="W94" s="3">
+        <v>-100</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-      <c r="AA94" s="3" t="s">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,67 +7267,70 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E100" s="3">
         <v>3200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4400</v>
       </c>
-      <c r="F100" s="3">
-        <v>100</v>
-      </c>
       <c r="G100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>5400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
-        <v>100</v>
-      </c>
       <c r="N100" s="3">
+        <v>100</v>
+      </c>
+      <c r="O100" s="3">
         <v>20200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>8800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>600</v>
       </c>
-      <c r="S100" s="3">
-        <v>100</v>
-      </c>
       <c r="T100" s="3">
+        <v>100</v>
+      </c>
+      <c r="U100" s="3">
         <v>200</v>
       </c>
-      <c r="U100" s="3">
-        <v>100</v>
-      </c>
       <c r="V100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
@@ -7093,16 +7339,19 @@
         <v>0</v>
       </c>
       <c r="Y100" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z100" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>100</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7154,12 +7403,12 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-      <c r="T101" s="3" t="s">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
         <v>0</v>
       </c>
@@ -7170,67 +7419,70 @@
         <v>0</v>
       </c>
       <c r="Y101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-6100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>18700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>8200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>400</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
         <v>0</v>
       </c>
@@ -7241,18 +7493,21 @@
         <v>0</v>
       </c>
       <c r="W102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-100</v>
       </c>
-      <c r="Z102" s="3">
-        <v>100</v>
-      </c>
       <c r="AA102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WKSP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WKSP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
   <si>
     <t>WKSP</t>
   </si>
@@ -656,146 +656,150 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>200</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
       <c r="J8" s="3">
         <v>0</v>
       </c>
@@ -812,16 +816,16 @@
         <v>0</v>
       </c>
       <c r="O8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P8" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q8" s="3">
         <v>200</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
       <c r="R8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3">
         <v>100</v>
@@ -830,52 +834,55 @@
         <v>100</v>
       </c>
       <c r="U8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
         <v>1900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>200</v>
       </c>
-      <c r="AA8" s="3">
-        <v>0</v>
-      </c>
       <c r="AB8" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>200</v>
       </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
       <c r="J9" s="3">
         <v>0</v>
       </c>
@@ -889,7 +896,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O9" s="3">
         <v>100</v>
@@ -910,22 +917,22 @@
         <v>100</v>
       </c>
       <c r="U9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V9" s="3">
+        <v>0</v>
+      </c>
+      <c r="W9" s="3">
         <v>1700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>700</v>
-      </c>
-      <c r="X9" s="3">
-        <v>400</v>
       </c>
       <c r="Y9" s="3">
         <v>400</v>
       </c>
       <c r="Z9" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="AA9" s="3">
         <v>100</v>
@@ -933,25 +940,28 @@
       <c r="AB9" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>200</v>
+      </c>
+      <c r="E10" s="3">
         <v>300</v>
       </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
       <c r="F10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3">
         <v>100</v>
       </c>
       <c r="H10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I10" s="3">
         <v>0</v>
@@ -969,20 +979,20 @@
         <v>0</v>
       </c>
       <c r="N10" s="3">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3">
         <v>-100</v>
       </c>
-      <c r="O10" s="3">
-        <v>0</v>
-      </c>
       <c r="P10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3">
+        <v>100</v>
+      </c>
+      <c r="R10" s="3">
         <v>-100</v>
       </c>
-      <c r="R10" s="3">
-        <v>0</v>
-      </c>
       <c r="S10" s="3">
         <v>0</v>
       </c>
@@ -993,28 +1003,31 @@
         <v>0</v>
       </c>
       <c r="V10" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="W10" s="3">
         <v>200</v>
       </c>
       <c r="X10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y10" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z10" s="3">
         <v>200</v>
       </c>
-      <c r="Z10" s="3">
-        <v>100</v>
-      </c>
       <c r="AA10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB10" s="3">
         <v>-100</v>
       </c>
-      <c r="AB10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1043,8 +1056,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1123,8 +1137,11 @@
       <c r="AB12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,35 +1220,38 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-300</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1251,25 +1271,25 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-200</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>4</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V14" s="3">
-        <v>-300</v>
+      <c r="V14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W14" s="3">
         <v>-300</v>
       </c>
       <c r="X14" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1280,34 +1300,37 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1363,8 +1386,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,88 +1416,92 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E17" s="3">
         <v>5800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4200</v>
-      </c>
-      <c r="F17" s="3">
-        <v>4400</v>
       </c>
       <c r="G17" s="3">
         <v>4400</v>
       </c>
       <c r="H17" s="3">
+        <v>4400</v>
+      </c>
+      <c r="I17" s="3">
         <v>3900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2100</v>
-      </c>
-      <c r="P17" s="3">
-        <v>1000</v>
       </c>
       <c r="Q17" s="3">
         <v>1000</v>
       </c>
       <c r="R17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S17" s="3">
         <v>300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>500</v>
-      </c>
-      <c r="T17" s="3">
-        <v>200</v>
       </c>
       <c r="U17" s="3">
         <v>200</v>
       </c>
       <c r="V17" s="3">
+        <v>200</v>
+      </c>
+      <c r="W17" s="3">
         <v>2200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1479,79 +1509,82 @@
         <v>-3900</v>
       </c>
       <c r="E18" s="3">
-        <v>-3700</v>
+        <v>-3900</v>
       </c>
       <c r="F18" s="3">
         <v>-3600</v>
       </c>
       <c r="G18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="H18" s="3">
         <v>-3900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3700</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-3600</v>
       </c>
       <c r="J18" s="3">
         <v>-3500</v>
       </c>
       <c r="K18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="L18" s="3">
         <v>-3000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>300</v>
       </c>
-      <c r="X18" s="3">
-        <v>0</v>
-      </c>
       <c r="Y18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-400</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-300</v>
       </c>
       <c r="AB18" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,43 +1613,44 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>200</v>
       </c>
       <c r="L20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M20" s="3">
         <v>100</v>
       </c>
       <c r="N20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
@@ -1658,95 +1692,101 @@
         <v>0</v>
       </c>
       <c r="AB20" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3400</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-3300</v>
       </c>
       <c r="H21" s="3">
         <v>-3300</v>
       </c>
       <c r="I21" s="3">
-        <v>-3200</v>
+        <v>-3400</v>
       </c>
       <c r="J21" s="3">
         <v>-3300</v>
       </c>
       <c r="K21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="L21" s="3">
         <v>-2400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-3800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-400</v>
-      </c>
-      <c r="T21" s="3">
-        <v>-100</v>
       </c>
       <c r="U21" s="3">
         <v>-100</v>
       </c>
       <c r="V21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W21" s="3">
         <v>-300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>300</v>
       </c>
-      <c r="X21" s="3">
-        <v>0</v>
-      </c>
       <c r="Y21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-500</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>-300</v>
       </c>
       <c r="AB21" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E22" s="3">
         <v>100</v>
@@ -1758,7 +1798,7 @@
         <v>100</v>
       </c>
       <c r="H22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I22" s="3">
         <v>200</v>
@@ -1767,14 +1807,14 @@
         <v>200</v>
       </c>
       <c r="K22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L22" s="3">
+        <v>100</v>
+      </c>
+      <c r="M22" s="3">
         <v>200</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -1785,25 +1825,25 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>200</v>
       </c>
-      <c r="R22" s="3">
-        <v>100</v>
-      </c>
       <c r="S22" s="3">
+        <v>100</v>
+      </c>
+      <c r="T22" s="3">
         <v>200</v>
       </c>
-      <c r="T22" s="3">
-        <v>100</v>
-      </c>
       <c r="U22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -1820,111 +1860,117 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4000</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-3700</v>
       </c>
       <c r="F23" s="3">
         <v>-3700</v>
       </c>
       <c r="G23" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="H23" s="3">
         <v>-3900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3800</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-3500</v>
       </c>
       <c r="J23" s="3">
         <v>-3500</v>
       </c>
       <c r="K23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="L23" s="3">
         <v>-2900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-600</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-200</v>
       </c>
       <c r="U23" s="3">
         <v>-200</v>
       </c>
       <c r="V23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W23" s="3">
         <v>-400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>300</v>
       </c>
-      <c r="X23" s="3">
-        <v>0</v>
-      </c>
       <c r="Y23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="3">
         <v>-100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-500</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-300</v>
       </c>
       <c r="AB23" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1980,8 +2026,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4000</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-3700</v>
       </c>
       <c r="F26" s="3">
         <v>-3700</v>
       </c>
       <c r="G26" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="H26" s="3">
         <v>-3900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3800</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-3500</v>
       </c>
       <c r="J26" s="3">
         <v>-3500</v>
       </c>
       <c r="K26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="L26" s="3">
         <v>-2900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-600</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-200</v>
       </c>
       <c r="U26" s="3">
         <v>-200</v>
       </c>
       <c r="V26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W26" s="3">
         <v>-400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>300</v>
       </c>
-      <c r="X26" s="3">
-        <v>0</v>
-      </c>
       <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3">
         <v>-100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-500</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-300</v>
       </c>
       <c r="AB26" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4000</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-3700</v>
       </c>
       <c r="F27" s="3">
         <v>-3700</v>
       </c>
       <c r="G27" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="H27" s="3">
         <v>-3900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3800</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-3500</v>
       </c>
       <c r="J27" s="3">
         <v>-3500</v>
       </c>
       <c r="K27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="L27" s="3">
         <v>-2900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-600</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-200</v>
       </c>
       <c r="U27" s="3">
         <v>-200</v>
       </c>
       <c r="V27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W27" s="3">
         <v>-400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>300</v>
       </c>
-      <c r="X27" s="3">
-        <v>0</v>
-      </c>
       <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="3">
         <v>-100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-500</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>-300</v>
       </c>
       <c r="AB27" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,43 +2607,46 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>-200</v>
       </c>
       <c r="L32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="M32" s="3">
         <v>-100</v>
       </c>
       <c r="N32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
@@ -2618,90 +2688,96 @@
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4000</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-3700</v>
       </c>
       <c r="F33" s="3">
         <v>-3700</v>
       </c>
       <c r="G33" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="H33" s="3">
         <v>-3900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3800</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-3500</v>
       </c>
       <c r="J33" s="3">
         <v>-3500</v>
       </c>
       <c r="K33" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="L33" s="3">
         <v>-2900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-600</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-200</v>
       </c>
       <c r="U33" s="3">
         <v>-200</v>
       </c>
       <c r="V33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W33" s="3">
         <v>-400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>300</v>
       </c>
-      <c r="X33" s="3">
-        <v>0</v>
-      </c>
       <c r="Y33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="3">
         <v>-100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-500</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>-300</v>
       </c>
       <c r="AB33" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4000</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-3700</v>
       </c>
       <c r="F35" s="3">
         <v>-3700</v>
       </c>
       <c r="G35" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="H35" s="3">
         <v>-3900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3800</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-3500</v>
       </c>
       <c r="J35" s="3">
         <v>-3500</v>
       </c>
       <c r="K35" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="L35" s="3">
         <v>-2900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-600</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-200</v>
       </c>
       <c r="U35" s="3">
         <v>-200</v>
       </c>
       <c r="V35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W35" s="3">
         <v>-400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>300</v>
       </c>
-      <c r="X35" s="3">
-        <v>0</v>
-      </c>
       <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="3">
         <v>-100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-500</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>-300</v>
       </c>
       <c r="AB35" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,62 +3091,63 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E41" s="3">
         <v>3400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>14600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>16700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>19100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>25800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>28600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>29000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>12300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>500</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
       <c r="U41" s="3">
         <v>0</v>
       </c>
@@ -3068,25 +3155,28 @@
         <v>0</v>
       </c>
       <c r="W41" s="3">
+        <v>0</v>
+      </c>
+      <c r="X41" s="3">
         <v>200</v>
       </c>
-      <c r="X41" s="3">
-        <v>100</v>
-      </c>
       <c r="Y41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z41" s="3">
         <v>0</v>
       </c>
       <c r="AA41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="3">
         <v>200</v>
       </c>
-      <c r="AB41" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3094,22 +3184,22 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3165,31 +3255,34 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>600</v>
+      </c>
+      <c r="E43" s="3">
         <v>800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>400</v>
-      </c>
-      <c r="J43" s="3">
-        <v>300</v>
       </c>
       <c r="K43" s="3">
         <v>300</v>
@@ -3198,25 +3291,25 @@
         <v>300</v>
       </c>
       <c r="M43" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="N43" s="3">
+        <v>100</v>
+      </c>
+      <c r="O43" s="3">
         <v>200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>200</v>
       </c>
-      <c r="Q43" s="3">
-        <v>100</v>
-      </c>
       <c r="R43" s="3">
+        <v>100</v>
+      </c>
+      <c r="S43" s="3">
         <v>300</v>
-      </c>
-      <c r="S43" s="3">
-        <v>200</v>
       </c>
       <c r="T43" s="3">
         <v>200</v>
@@ -3225,67 +3318,70 @@
         <v>200</v>
       </c>
       <c r="V43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W43" s="3">
+        <v>100</v>
+      </c>
+      <c r="X43" s="3">
         <v>200</v>
       </c>
-      <c r="X43" s="3">
-        <v>100</v>
-      </c>
       <c r="Y43" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z43" s="3">
         <v>400</v>
       </c>
-      <c r="Z43" s="3">
-        <v>100</v>
-      </c>
       <c r="AA43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB43" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E44" s="3">
         <v>6400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6500</v>
-      </c>
-      <c r="F44" s="3">
-        <v>3600</v>
       </c>
       <c r="G44" s="3">
         <v>3600</v>
       </c>
       <c r="H44" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I44" s="3">
         <v>2900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1600</v>
-      </c>
-      <c r="J44" s="3">
-        <v>1300</v>
       </c>
       <c r="K44" s="3">
         <v>1300</v>
       </c>
       <c r="L44" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M44" s="3">
         <v>1100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>500</v>
       </c>
-      <c r="O44" s="3">
-        <v>100</v>
-      </c>
       <c r="P44" s="3">
         <v>100</v>
       </c>
@@ -3293,10 +3389,10 @@
         <v>100</v>
       </c>
       <c r="R44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T44" s="3">
         <v>100</v>
@@ -3308,87 +3404,90 @@
         <v>100</v>
       </c>
       <c r="W44" s="3">
+        <v>100</v>
+      </c>
+      <c r="X44" s="3">
         <v>200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>300</v>
       </c>
-      <c r="AA44" s="3">
-        <v>100</v>
-      </c>
       <c r="AB44" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="M45" s="3">
+        <v>5100</v>
+      </c>
+      <c r="N45" s="3">
+        <v>4100</v>
+      </c>
+      <c r="O45" s="3">
+        <v>4700</v>
+      </c>
+      <c r="P45" s="3">
+        <v>7400</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>600</v>
+      </c>
+      <c r="R45" s="3">
+        <v>300</v>
+      </c>
+      <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="T45" s="3">
+        <v>100</v>
+      </c>
+      <c r="U45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>700</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>2200</v>
-      </c>
-      <c r="J45" s="3">
-        <v>2000</v>
-      </c>
-      <c r="K45" s="3">
-        <v>3700</v>
-      </c>
-      <c r="L45" s="3">
-        <v>5100</v>
-      </c>
-      <c r="M45" s="3">
-        <v>4100</v>
-      </c>
-      <c r="N45" s="3">
-        <v>4700</v>
-      </c>
-      <c r="O45" s="3">
-        <v>7400</v>
-      </c>
-      <c r="P45" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>300</v>
-      </c>
-      <c r="R45" s="3">
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3">
-        <v>100</v>
-      </c>
-      <c r="T45" s="3">
-        <v>300</v>
-      </c>
-      <c r="U45" s="3">
-        <v>200</v>
-      </c>
-      <c r="V45" s="3">
-        <v>100</v>
-      </c>
       <c r="W45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X45" s="3">
         <v>0</v>
@@ -3397,81 +3496,84 @@
         <v>0</v>
       </c>
       <c r="Z45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB45" s="3">
         <v>400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>10700</v>
+        <v>8900</v>
       </c>
       <c r="E46" s="3">
         <v>10700</v>
       </c>
       <c r="F46" s="3">
+        <v>10700</v>
+      </c>
+      <c r="G46" s="3">
         <v>9100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>22100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>25700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>30800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>34000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>36800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>13100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>900</v>
-      </c>
-      <c r="T46" s="3">
-        <v>500</v>
       </c>
       <c r="U46" s="3">
         <v>500</v>
       </c>
       <c r="V46" s="3">
+        <v>500</v>
+      </c>
+      <c r="W46" s="3">
         <v>300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>700</v>
-      </c>
-      <c r="X46" s="3">
-        <v>500</v>
       </c>
       <c r="Y46" s="3">
         <v>500</v>
@@ -3480,13 +3582,16 @@
         <v>500</v>
       </c>
       <c r="AA46" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB46" s="3">
         <v>700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3509,7 +3614,7 @@
         <v>100</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3550,8 +3655,8 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>4</v>
+      <c r="X47" s="3">
+        <v>0</v>
       </c>
       <c r="Y47" s="3" t="s">
         <v>4</v>
@@ -3565,56 +3670,59 @@
       <c r="AB47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E48" s="3">
         <v>15000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>15300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>15100</v>
       </c>
-      <c r="I48" s="3">
-        <v>14000</v>
-      </c>
       <c r="J48" s="3">
+        <v>13400</v>
+      </c>
+      <c r="K48" s="3">
         <v>13100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>200</v>
       </c>
-      <c r="R48" s="3">
-        <v>100</v>
-      </c>
       <c r="S48" s="3">
         <v>100</v>
       </c>
@@ -3625,13 +3733,13 @@
         <v>100</v>
       </c>
       <c r="V48" s="3">
+        <v>100</v>
+      </c>
+      <c r="W48" s="3">
         <v>200</v>
       </c>
-      <c r="W48" s="3">
-        <v>100</v>
-      </c>
       <c r="X48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y48" s="3">
         <v>0</v>
@@ -3645,8 +3753,11 @@
       <c r="AB48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3672,26 +3783,26 @@
         <v>1300</v>
       </c>
       <c r="K49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L49" s="3">
         <v>1000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>300</v>
       </c>
-      <c r="Q49" s="3">
-        <v>100</v>
-      </c>
       <c r="R49" s="3">
         <v>100</v>
       </c>
@@ -3708,7 +3819,7 @@
         <v>100</v>
       </c>
       <c r="W49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
@@ -3725,8 +3836,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,8 +4002,11 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3909,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3944,8 +4064,8 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>4</v>
+      <c r="V52" s="3">
+        <v>0</v>
       </c>
       <c r="W52" s="3" t="s">
         <v>4</v>
@@ -3956,17 +4076,20 @@
       <c r="Y52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z52" s="3">
-        <v>0</v>
+      <c r="Z52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,73 +4168,76 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E54" s="3">
         <v>27200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>27300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>26000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>24600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>30100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>32800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>35700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>38200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>34000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>36300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>38600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1100</v>
-      </c>
-      <c r="T54" s="3">
-        <v>700</v>
       </c>
       <c r="U54" s="3">
         <v>700</v>
       </c>
       <c r="V54" s="3">
+        <v>700</v>
+      </c>
+      <c r="W54" s="3">
         <v>500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>800</v>
-      </c>
-      <c r="X54" s="3">
-        <v>600</v>
       </c>
       <c r="Y54" s="3">
         <v>600</v>
@@ -4120,13 +4246,16 @@
         <v>600</v>
       </c>
       <c r="AA54" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB54" s="3">
         <v>700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,58 +4315,59 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E57" s="3">
         <v>1800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1200</v>
-      </c>
-      <c r="I57" s="3">
-        <v>2000</v>
       </c>
       <c r="J57" s="3">
         <v>2000</v>
       </c>
       <c r="K57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L57" s="3">
         <v>1800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>900</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>1000</v>
       </c>
       <c r="R57" s="3">
         <v>1000</v>
       </c>
       <c r="S57" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="T57" s="3">
         <v>900</v>
@@ -4245,54 +4376,57 @@
         <v>900</v>
       </c>
       <c r="V57" s="3">
+        <v>900</v>
+      </c>
+      <c r="W57" s="3">
         <v>1000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>900</v>
-      </c>
-      <c r="X57" s="3">
-        <v>600</v>
       </c>
       <c r="Y57" s="3">
         <v>600</v>
       </c>
       <c r="Z57" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA57" s="3">
         <v>400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E58" s="3">
-        <v>5300</v>
+        <v>200</v>
       </c>
       <c r="F58" s="3">
-        <v>5300</v>
+        <v>5600</v>
       </c>
       <c r="G58" s="3">
-        <v>5300</v>
+        <v>5600</v>
       </c>
       <c r="H58" s="3">
-        <v>5300</v>
+        <v>5600</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="L58" s="3">
         <v>300</v>
@@ -4313,19 +4447,19 @@
         <v>300</v>
       </c>
       <c r="R58" s="3">
+        <v>300</v>
+      </c>
+      <c r="S58" s="3">
         <v>700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>400</v>
-      </c>
-      <c r="V58" s="3">
-        <v>300</v>
       </c>
       <c r="W58" s="3">
         <v>300</v>
@@ -4345,31 +4479,34 @@
       <c r="AB58" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>500</v>
-      </c>
-      <c r="E59" s="3">
-        <v>300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>400</v>
-      </c>
-      <c r="G59" s="3">
-        <v>400</v>
-      </c>
-      <c r="H59" s="3">
-        <v>400</v>
-      </c>
-      <c r="I59" s="3">
-        <v>400</v>
-      </c>
-      <c r="J59" s="3">
-        <v>400</v>
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K59" s="3">
         <v>400</v>
@@ -4378,10 +4515,10 @@
         <v>400</v>
       </c>
       <c r="M59" s="3">
+        <v>400</v>
+      </c>
+      <c r="N59" s="3">
         <v>200</v>
-      </c>
-      <c r="N59" s="3">
-        <v>300</v>
       </c>
       <c r="O59" s="3">
         <v>300</v>
@@ -4390,146 +4527,152 @@
         <v>300</v>
       </c>
       <c r="Q59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="R59" s="3">
         <v>100</v>
       </c>
       <c r="S59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T59" s="3">
         <v>0</v>
       </c>
       <c r="U59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V59" s="3">
         <v>100</v>
       </c>
       <c r="W59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X59" s="3">
         <v>0</v>
       </c>
       <c r="Y59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z59" s="3">
         <v>100</v>
       </c>
       <c r="AA59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2400</v>
-      </c>
-      <c r="J60" s="3">
-        <v>2500</v>
       </c>
       <c r="K60" s="3">
         <v>2500</v>
       </c>
       <c r="L60" s="3">
+        <v>2500</v>
+      </c>
+      <c r="M60" s="3">
         <v>2400</v>
-      </c>
-      <c r="M60" s="3">
-        <v>1800</v>
       </c>
       <c r="N60" s="3">
         <v>1800</v>
       </c>
       <c r="O60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P60" s="3">
         <v>1700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1200</v>
-      </c>
-      <c r="X60" s="3">
-        <v>900</v>
       </c>
       <c r="Y60" s="3">
         <v>900</v>
       </c>
       <c r="Z60" s="3">
+        <v>900</v>
+      </c>
+      <c r="AA60" s="3">
         <v>800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>5300</v>
+        <v>5600</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I61" s="3">
-        <v>5300</v>
+        <v>700</v>
       </c>
       <c r="J61" s="3">
-        <v>5300</v>
+        <v>6100</v>
       </c>
       <c r="K61" s="3">
         <v>5300</v>
@@ -4538,7 +4681,7 @@
         <v>5300</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="N61" s="3">
         <v>0</v>
@@ -4585,52 +4728,55 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>500</v>
-      </c>
-      <c r="E62" s="3">
-        <v>500</v>
-      </c>
-      <c r="F62" s="3">
-        <v>600</v>
-      </c>
-      <c r="G62" s="3">
-        <v>600</v>
-      </c>
-      <c r="H62" s="3">
-        <v>700</v>
-      </c>
-      <c r="I62" s="3">
-        <v>800</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1100</v>
-      </c>
-      <c r="M62" s="3">
-        <v>300</v>
       </c>
       <c r="N62" s="3">
         <v>300</v>
       </c>
       <c r="O62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="P62" s="3">
         <v>400</v>
       </c>
       <c r="Q62" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -4650,8 +4796,8 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>4</v>
+      <c r="X62" s="3">
+        <v>0</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>4</v>
@@ -4665,8 +4811,11 @@
       <c r="AB62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,40 +5060,43 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E66" s="3">
         <v>8000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8600</v>
-      </c>
-      <c r="K66" s="3">
-        <v>8800</v>
       </c>
       <c r="L66" s="3">
         <v>8800</v>
       </c>
       <c r="M66" s="3">
-        <v>2100</v>
+        <v>8800</v>
       </c>
       <c r="N66" s="3">
         <v>2100</v>
@@ -4947,46 +5105,49 @@
         <v>2100</v>
       </c>
       <c r="P66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Q66" s="3">
         <v>1900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1500</v>
-      </c>
-      <c r="U66" s="3">
-        <v>1400</v>
       </c>
       <c r="V66" s="3">
         <v>1400</v>
       </c>
       <c r="W66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="X66" s="3">
         <v>1300</v>
-      </c>
-      <c r="X66" s="3">
-        <v>900</v>
       </c>
       <c r="Y66" s="3">
         <v>900</v>
       </c>
       <c r="Z66" s="3">
+        <v>900</v>
+      </c>
+      <c r="AA66" s="3">
         <v>800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,88 +5506,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-60200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-56000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-52000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-48300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-44700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-40700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-36900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-33400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-29900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-27000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-23700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-20800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-17100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-14900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-14100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-12900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-12600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-12000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-11000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-10800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-10200</v>
-      </c>
-      <c r="X72" s="3">
-        <v>-10500</v>
       </c>
       <c r="Y72" s="3">
         <v>-10500</v>
       </c>
       <c r="Z72" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="AA72" s="3">
         <v>-10400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-9900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,88 +5838,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E76" s="3">
         <v>19100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>19400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>21600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>24100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>26900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>29400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>31900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>34200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>36500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-400</v>
-      </c>
-      <c r="X76" s="3">
-        <v>-300</v>
       </c>
       <c r="Y76" s="3">
         <v>-300</v>
       </c>
       <c r="Z76" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AA76" s="3">
         <v>-200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4000</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-3700</v>
       </c>
       <c r="F81" s="3">
         <v>-3700</v>
       </c>
       <c r="G81" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="H81" s="3">
         <v>-3900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3800</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-3500</v>
       </c>
       <c r="J81" s="3">
         <v>-3500</v>
       </c>
       <c r="K81" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="L81" s="3">
         <v>-2900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-600</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-200</v>
       </c>
       <c r="U81" s="3">
         <v>-200</v>
       </c>
       <c r="V81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W81" s="3">
         <v>-400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>300</v>
       </c>
-      <c r="X81" s="3">
-        <v>0</v>
-      </c>
       <c r="Y81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="3">
         <v>-100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-500</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>-300</v>
       </c>
       <c r="AB81" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,40 +6208,41 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>300</v>
+      </c>
+      <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
         <v>400</v>
       </c>
-      <c r="F83" s="3">
-        <v>100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>600</v>
-      </c>
-      <c r="H83" s="3">
-        <v>300</v>
-      </c>
       <c r="I83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
         <v>400</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N83" s="3">
         <v>100</v>
@@ -6052,7 +6251,7 @@
         <v>100</v>
       </c>
       <c r="P83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -6090,8 +6289,11 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,88 +6704,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3000</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-2000</v>
       </c>
       <c r="N89" s="3">
         <v>-2000</v>
       </c>
       <c r="O89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="P89" s="3">
         <v>-1000</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-500</v>
       </c>
       <c r="Q89" s="3">
         <v>-500</v>
       </c>
       <c r="R89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="S89" s="3">
         <v>-300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-200</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
         <v>-200</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
         <v>200</v>
       </c>
-      <c r="X89" s="3">
-        <v>100</v>
-      </c>
       <c r="Y89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-100</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,58 +6820,59 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-200</v>
       </c>
       <c r="F91" s="3">
         <v>-200</v>
       </c>
       <c r="G91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H91" s="3">
         <v>-800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>4</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>4</v>
@@ -6659,14 +6880,14 @@
       <c r="U91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V91" s="3">
-        <v>-100</v>
+      <c r="V91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>4</v>
+      <c r="X91" s="3">
+        <v>-100</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>4</v>
@@ -6680,8 +6901,11 @@
       <c r="AB91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,56 +7067,59 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-200</v>
       </c>
       <c r="F94" s="3">
         <v>-200</v>
       </c>
       <c r="G94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H94" s="3">
         <v>-800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
@@ -6900,28 +7130,31 @@
         <v>0</v>
       </c>
       <c r="V94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>4</v>
+      <c r="X94" s="3">
+        <v>-100</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Z94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,31 +7183,32 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,70 +7513,73 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>3600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4400</v>
       </c>
-      <c r="G100" s="3">
-        <v>100</v>
-      </c>
       <c r="H100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>5400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
-        <v>100</v>
-      </c>
       <c r="O100" s="3">
+        <v>100</v>
+      </c>
+      <c r="P100" s="3">
         <v>20200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>8800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>600</v>
       </c>
-      <c r="T100" s="3">
-        <v>100</v>
-      </c>
       <c r="U100" s="3">
+        <v>100</v>
+      </c>
+      <c r="V100" s="3">
         <v>200</v>
       </c>
-      <c r="V100" s="3">
-        <v>100</v>
-      </c>
       <c r="W100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X100" s="3">
         <v>0</v>
@@ -7342,39 +7588,42 @@
         <v>0</v>
       </c>
       <c r="Z100" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA100" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
+        <v>100</v>
       </c>
       <c r="AB100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7406,11 +7655,11 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
@@ -7422,70 +7671,73 @@
         <v>0</v>
       </c>
       <c r="Z101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>18700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>8200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>400</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3">
         <v>0</v>
       </c>
@@ -7496,18 +7748,21 @@
         <v>0</v>
       </c>
       <c r="X102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-100</v>
       </c>
-      <c r="AA102" s="3">
-        <v>100</v>
-      </c>
       <c r="AB102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WKSP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WKSP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="92">
   <si>
     <t>WKSP</t>
   </si>
@@ -656,156 +656,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F8" s="3">
         <v>3100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1900</v>
-      </c>
-      <c r="F8" s="3">
-        <v>500</v>
-      </c>
-      <c r="G8" s="3">
-        <v>800</v>
       </c>
       <c r="H8" s="3">
         <v>500</v>
       </c>
       <c r="I8" s="3">
+        <v>800</v>
+      </c>
+      <c r="J8" s="3">
+        <v>500</v>
+      </c>
+      <c r="K8" s="3">
         <v>200</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
       <c r="L8" s="3">
         <v>0</v>
       </c>
@@ -819,76 +826,82 @@
         <v>0</v>
       </c>
       <c r="P8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>100</v>
+      </c>
+      <c r="S8" s="3">
         <v>200</v>
       </c>
-      <c r="R8" s="3">
-        <v>0</v>
-      </c>
-      <c r="S8" s="3">
-        <v>100</v>
-      </c>
       <c r="T8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U8" s="3">
         <v>100</v>
       </c>
       <c r="V8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W8" s="3">
+        <v>100</v>
+      </c>
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
         <v>1900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>200</v>
       </c>
-      <c r="AB8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F9" s="3">
         <v>2900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>200</v>
       </c>
-      <c r="J9" s="3">
-        <v>0</v>
-      </c>
-      <c r="K9" s="3">
-        <v>0</v>
-      </c>
       <c r="L9" s="3">
         <v>0</v>
       </c>
@@ -899,10 +912,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="3">
         <v>100</v>
@@ -920,54 +933,60 @@
         <v>100</v>
       </c>
       <c r="V9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W9" s="3">
+        <v>100</v>
+      </c>
+      <c r="X9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
         <v>1700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>400</v>
       </c>
-      <c r="AA9" s="3">
-        <v>100</v>
-      </c>
-      <c r="AB9" s="3">
-        <v>100</v>
-      </c>
       <c r="AC9" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE9" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E10" s="3">
         <v>300</v>
       </c>
       <c r="F10" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G10" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -982,23 +1001,23 @@
         <v>0</v>
       </c>
       <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
         <v>-100</v>
       </c>
-      <c r="P10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>100</v>
-      </c>
       <c r="R10" s="3">
+        <v>0</v>
+      </c>
+      <c r="S10" s="3">
+        <v>100</v>
+      </c>
+      <c r="T10" s="3">
         <v>-100</v>
       </c>
-      <c r="S10" s="3">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3">
-        <v>0</v>
-      </c>
       <c r="U10" s="3">
         <v>0</v>
       </c>
@@ -1006,13 +1025,13 @@
         <v>0</v>
       </c>
       <c r="W10" s="3">
+        <v>0</v>
+      </c>
+      <c r="X10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
         <v>200</v>
-      </c>
-      <c r="X10" s="3">
-        <v>200</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>100</v>
       </c>
       <c r="Z10" s="3">
         <v>200</v>
@@ -1021,13 +1040,19 @@
         <v>100</v>
       </c>
       <c r="AB10" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD10" s="3">
         <v>-100</v>
       </c>
-      <c r="AC10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,16 +1082,18 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>4</v>
+      <c r="D12" s="3">
+        <v>400</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2300</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>4</v>
@@ -1077,8 +1104,8 @@
       <c r="H12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>4</v>
+      <c r="I12" s="3">
+        <v>1700</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>4</v>
@@ -1140,8 +1167,14 @@
       <c r="AC12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,8 +1256,14 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1237,27 +1276,27 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-300</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1274,40 +1313,46 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-200</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>-300</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1315,29 +1360,29 @@
         <v>400</v>
       </c>
       <c r="E15" s="3">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="F15" s="3">
         <v>400</v>
       </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
+        <v>400</v>
+      </c>
+      <c r="I15" s="3">
+        <v>100</v>
+      </c>
+      <c r="J15" s="3">
         <v>600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>200</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1389,8 +1434,14 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1468,188 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E17" s="3">
         <v>7000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
+        <v>7000</v>
+      </c>
+      <c r="G17" s="3">
         <v>5800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>4200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>4400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>4400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>3900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>3300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>3700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>2200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-3900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-3600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-3500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-3900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-3700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-3500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-3500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-3000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-3300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-2800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-3700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-1000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>300</v>
       </c>
-      <c r="Y18" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,8 +1679,10 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1623,40 +1690,40 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
-        <v>100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>100</v>
-      </c>
       <c r="O20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -1695,27 +1762,33 @@
         <v>0</v>
       </c>
       <c r="AC20" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-3500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-3600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-3200</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-3300</v>
       </c>
       <c r="I21" s="3">
         <v>-3400</v>
@@ -1724,64 +1797,70 @@
         <v>-3300</v>
       </c>
       <c r="K21" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="L21" s="3">
         <v>-3300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="N21" s="3">
         <v>-2400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-3200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-2700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-3800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-1000</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-100</v>
-      </c>
-      <c r="T21" s="3">
-        <v>-400</v>
       </c>
       <c r="U21" s="3">
         <v>-100</v>
       </c>
       <c r="V21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="W21" s="3">
         <v>-100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>300</v>
       </c>
-      <c r="Y21" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1789,10 +1868,10 @@
         <v>200</v>
       </c>
       <c r="E22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G22" s="3">
         <v>100</v>
@@ -1801,25 +1880,25 @@
         <v>100</v>
       </c>
       <c r="I22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K22" s="3">
         <v>200</v>
       </c>
       <c r="L22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M22" s="3">
         <v>200</v>
       </c>
       <c r="N22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1828,10 +1907,10 @@
         <v>0</v>
       </c>
       <c r="R22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="S22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T22" s="3">
         <v>200</v>
@@ -1840,7 +1919,7 @@
         <v>100</v>
       </c>
       <c r="V22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="W22" s="3">
         <v>100</v>
@@ -1849,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="Y22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -1863,91 +1942,103 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-4100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-4000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-3700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-3700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-3900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-3800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-3500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-3500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-2900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-3400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-2800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-3800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-1200</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-200</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-600</v>
       </c>
       <c r="U23" s="3">
         <v>-200</v>
       </c>
       <c r="V23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="W23" s="3">
         <v>-200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>300</v>
       </c>
-      <c r="Y23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="3">
         <v>-100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1972,11 +2063,11 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2029,8 +2120,14 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2209,192 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-4100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-4000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-3700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-3700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-3900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-3800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-3500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-3500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-2900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-3400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-2800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-3800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-1200</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-600</v>
       </c>
       <c r="U26" s="3">
         <v>-200</v>
       </c>
       <c r="V26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="W26" s="3">
         <v>-200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>300</v>
       </c>
-      <c r="Y26" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="3">
         <v>-100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-4100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-4000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-3700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-3700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-3900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-3800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-3500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-3500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-2900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-3400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-2800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-3800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-1200</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-600</v>
       </c>
       <c r="U27" s="3">
         <v>-200</v>
       </c>
       <c r="V27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="W27" s="3">
         <v>-200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>300</v>
       </c>
-      <c r="Y27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2476,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2565,14 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2654,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,8 +2743,14 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2619,41 +2758,41 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>100</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2691,93 +2830,105 @@
         <v>0</v>
       </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-4100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-4000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-3700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-3700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-3900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-3800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-3500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-3500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-2900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-3400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-2800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-3800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-1200</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-600</v>
       </c>
       <c r="U33" s="3">
         <v>-200</v>
       </c>
       <c r="V33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="W33" s="3">
         <v>-200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>300</v>
       </c>
-      <c r="Y33" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +3010,197 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-4100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-4000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-3700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-3700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-3900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-3800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-3500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-3500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-2900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-3400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-2800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-3800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-1200</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-600</v>
       </c>
       <c r="U35" s="3">
         <v>-200</v>
       </c>
       <c r="V35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="W35" s="3">
         <v>-200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>300</v>
       </c>
-      <c r="Y35" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3230,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,91 +3263,99 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F41" s="3">
         <v>1900</v>
-      </c>
-      <c r="E41" s="3">
-        <v>3400</v>
-      </c>
-      <c r="F41" s="3">
-        <v>3500</v>
       </c>
       <c r="G41" s="3">
         <v>3400</v>
       </c>
       <c r="H41" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I41" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J41" s="3">
         <v>3000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>5900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>10500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>14600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>16700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>19100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>25800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>28600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>29000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>12300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>9300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>500</v>
       </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
-      <c r="V41" s="3">
-        <v>0</v>
-      </c>
       <c r="W41" s="3">
         <v>0</v>
       </c>
       <c r="X41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="3">
         <v>200</v>
       </c>
-      <c r="Y41" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>0</v>
-      </c>
       <c r="AA41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="3">
         <v>200</v>
       </c>
-      <c r="AC41" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3187,26 +3366,26 @@
         <v>100</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>100</v>
+      </c>
+      <c r="H42" s="3">
         <v>300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>1500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>1500</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3258,70 +3437,76 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>200</v>
+      </c>
+      <c r="F43" s="3">
         <v>600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>300</v>
-      </c>
-      <c r="G43" s="3">
-        <v>600</v>
-      </c>
-      <c r="H43" s="3">
-        <v>700</v>
       </c>
       <c r="I43" s="3">
         <v>600</v>
       </c>
       <c r="J43" s="3">
+        <v>700</v>
+      </c>
+      <c r="K43" s="3">
+        <v>600</v>
+      </c>
+      <c r="L43" s="3">
         <v>400</v>
-      </c>
-      <c r="K43" s="3">
-        <v>300</v>
-      </c>
-      <c r="L43" s="3">
-        <v>300</v>
       </c>
       <c r="M43" s="3">
         <v>300</v>
       </c>
       <c r="N43" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="P43" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Q43" s="3">
         <v>200</v>
       </c>
       <c r="R43" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="S43" s="3">
+        <v>200</v>
+      </c>
+      <c r="T43" s="3">
+        <v>100</v>
+      </c>
+      <c r="U43" s="3">
         <v>300</v>
-      </c>
-      <c r="T43" s="3">
-        <v>200</v>
-      </c>
-      <c r="U43" s="3">
-        <v>200</v>
       </c>
       <c r="V43" s="3">
         <v>200</v>
       </c>
       <c r="W43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X43" s="3">
         <v>200</v>
@@ -3330,75 +3515,81 @@
         <v>100</v>
       </c>
       <c r="Z43" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA43" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB43" s="3">
         <v>400</v>
       </c>
-      <c r="AA43" s="3">
-        <v>100</v>
-      </c>
-      <c r="AB43" s="3">
-        <v>0</v>
-      </c>
       <c r="AC43" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F44" s="3">
         <v>6100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>6400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>6500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>3600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>3600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>2900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>500</v>
       </c>
-      <c r="P44" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>100</v>
-      </c>
       <c r="R44" s="3">
         <v>100</v>
       </c>
       <c r="S44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T44" s="3">
         <v>100</v>
       </c>
       <c r="U44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V44" s="3">
         <v>100</v>
@@ -3407,10 +3598,10 @@
         <v>100</v>
       </c>
       <c r="X44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y44" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Z44" s="3">
         <v>200</v>
@@ -3419,13 +3610,19 @@
         <v>300</v>
       </c>
       <c r="AB44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC44" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+      <c r="AD44" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3450,148 +3647,160 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>2000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>3700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>5100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>4100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>4700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>7400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="T45" s="3">
-        <v>100</v>
-      </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
+        <v>100</v>
+      </c>
+      <c r="W45" s="3">
         <v>300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>200</v>
       </c>
-      <c r="W45" s="3">
-        <v>100</v>
-      </c>
-      <c r="X45" s="3">
-        <v>0</v>
-      </c>
       <c r="Y45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z45" s="3">
         <v>0</v>
       </c>
       <c r="AA45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD45" s="3">
         <v>400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>10500</v>
+      </c>
+      <c r="F46" s="3">
         <v>8900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>10700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>10700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>9100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>7900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>10500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>14700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>18300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>22100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>25700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>30800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>34000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>36800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>13100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>9800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>700</v>
-      </c>
-      <c r="Y46" s="3">
-        <v>500</v>
-      </c>
-      <c r="Z46" s="3">
-        <v>500</v>
       </c>
       <c r="AA46" s="3">
         <v>500</v>
       </c>
       <c r="AB46" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC46" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD46" s="3">
         <v>700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3617,10 +3826,10 @@
         <v>100</v>
       </c>
       <c r="K47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3658,11 +3867,11 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z47" s="3" t="s">
-        <v>4</v>
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>0</v>
       </c>
       <c r="AA47" s="3" t="s">
         <v>4</v>
@@ -3673,62 +3882,68 @@
       <c r="AC47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>14200</v>
+      </c>
+      <c r="F48" s="3">
         <v>14600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>15000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>15100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>15400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>15300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>15100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>13400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>13100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>12600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>11700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>200</v>
       </c>
-      <c r="S48" s="3">
-        <v>100</v>
-      </c>
-      <c r="T48" s="3">
-        <v>100</v>
-      </c>
       <c r="U48" s="3">
         <v>100</v>
       </c>
@@ -3736,16 +3951,16 @@
         <v>100</v>
       </c>
       <c r="W48" s="3">
+        <v>100</v>
+      </c>
+      <c r="X48" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y48" s="3">
         <v>200</v>
       </c>
-      <c r="X48" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>0</v>
-      </c>
       <c r="Z48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA48" s="3">
         <v>0</v>
@@ -3756,16 +3971,22 @@
       <c r="AC48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="E49" s="3">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="F49" s="3">
         <v>1300</v>
@@ -3786,29 +4007,29 @@
         <v>1300</v>
       </c>
       <c r="L49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N49" s="3">
         <v>1000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>300</v>
       </c>
-      <c r="R49" s="3">
-        <v>100</v>
-      </c>
-      <c r="S49" s="3">
-        <v>100</v>
-      </c>
       <c r="T49" s="3">
         <v>100</v>
       </c>
@@ -3822,10 +4043,10 @@
         <v>100</v>
       </c>
       <c r="X49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z49" s="3">
         <v>0</v>
@@ -3839,8 +4060,14 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4149,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,16 +4238,22 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
@@ -4025,18 +4264,18 @@
       <c r="H52" s="3">
         <v>0</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>600</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -4067,11 +4306,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X52" s="3" t="s">
-        <v>4</v>
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3">
+        <v>0</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>4</v>
@@ -4079,17 +4318,23 @@
       <c r="Z52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,91 +4416,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>25700</v>
+      </c>
+      <c r="F54" s="3">
         <v>24900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>27200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>27300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>26000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>24600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>27000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>30100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>32800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>35700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>38200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>34000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>36300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>38600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>14400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>10200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>800</v>
-      </c>
-      <c r="Y54" s="3">
-        <v>600</v>
-      </c>
-      <c r="Z54" s="3">
-        <v>600</v>
       </c>
       <c r="AA54" s="3">
         <v>600</v>
       </c>
       <c r="AB54" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC54" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD54" s="3">
         <v>700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4542,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,123 +4575,131 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F57" s="3">
         <v>2500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2300</v>
       </c>
-      <c r="G57" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J57" s="3">
         <v>1900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1000</v>
-      </c>
-      <c r="T57" s="3">
-        <v>900</v>
-      </c>
-      <c r="U57" s="3">
-        <v>900</v>
       </c>
       <c r="V57" s="3">
         <v>900</v>
       </c>
       <c r="W57" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="X57" s="3">
         <v>900</v>
       </c>
       <c r="Y57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Z57" s="3">
+        <v>900</v>
+      </c>
+      <c r="AA57" s="3">
         <v>600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>500</v>
+      </c>
+      <c r="F58" s="3">
         <v>400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>200</v>
-      </c>
-      <c r="F58" s="3">
-        <v>5600</v>
-      </c>
-      <c r="G58" s="3">
-        <v>5600</v>
       </c>
       <c r="H58" s="3">
         <v>5600</v>
       </c>
       <c r="I58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="J58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="K58" s="3">
         <v>5700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>400</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>300</v>
-      </c>
       <c r="M58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="N58" s="3">
         <v>300</v>
@@ -4450,22 +4717,22 @@
         <v>300</v>
       </c>
       <c r="S58" s="3">
+        <v>300</v>
+      </c>
+      <c r="T58" s="3">
+        <v>300</v>
+      </c>
+      <c r="U58" s="3">
         <v>700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>400</v>
-      </c>
-      <c r="W58" s="3">
-        <v>300</v>
-      </c>
-      <c r="X58" s="3">
-        <v>300</v>
       </c>
       <c r="Y58" s="3">
         <v>300</v>
@@ -4482,8 +4749,14 @@
       <c r="AC58" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4508,186 +4781,198 @@
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
-        <v>400</v>
-      </c>
-      <c r="L59" s="3">
-        <v>400</v>
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M59" s="3">
         <v>400</v>
       </c>
       <c r="N59" s="3">
+        <v>400</v>
+      </c>
+      <c r="O59" s="3">
+        <v>400</v>
+      </c>
+      <c r="P59" s="3">
         <v>200</v>
-      </c>
-      <c r="O59" s="3">
-        <v>300</v>
-      </c>
-      <c r="P59" s="3">
-        <v>300</v>
       </c>
       <c r="Q59" s="3">
         <v>300</v>
       </c>
       <c r="R59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="S59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="T59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AD59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F60" s="3">
         <v>3000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>7800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>7200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>7600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>1200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F61" s="3">
         <v>5600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>5800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>6100</v>
-      </c>
-      <c r="K61" s="3">
-        <v>5300</v>
-      </c>
-      <c r="L61" s="3">
-        <v>5300</v>
       </c>
       <c r="M61" s="3">
         <v>5300</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
@@ -4731,8 +5016,14 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4757,33 +5048,33 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>400</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
-      </c>
-      <c r="S62" s="3">
-        <v>0</v>
-      </c>
       <c r="T62" s="3">
         <v>0</v>
       </c>
@@ -4799,11 +5090,11 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z62" s="3" t="s">
-        <v>4</v>
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>0</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>4</v>
@@ -4814,8 +5105,14 @@
       <c r="AC62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5194,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5283,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,91 +5372,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>8300</v>
+      </c>
+      <c r="F66" s="3">
         <v>8600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>8000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>8400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>7800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>8200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>7600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>8500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>8600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>8800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>8800</v>
-      </c>
-      <c r="N66" s="3">
-        <v>2100</v>
-      </c>
-      <c r="O66" s="3">
-        <v>2100</v>
       </c>
       <c r="P66" s="3">
         <v>2100</v>
       </c>
       <c r="Q66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="R66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="S66" s="3">
         <v>1900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5498,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5583,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5672,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5761,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,91 +5850,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-68900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-64500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-60200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-56000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-52000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-48300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-44700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-40700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-36900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-33400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-29900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-27000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-23700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-20800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-17100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-14900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-14100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-12900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-12600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-12000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-11000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-10800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-10500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-10500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-10400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-9900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +6028,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +6117,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,91 +6206,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>17400</v>
+      </c>
+      <c r="F76" s="3">
         <v>16400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>19100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>18900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>18200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>16400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>19400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>21600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>24100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>26900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>29400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>31900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>34200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>36500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>12500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>8800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>-800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>-700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>-900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>-400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>-300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>-200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>-500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6384,197 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-4100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-4000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-3700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-3700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-3900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-3800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-3500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-3500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-2900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-3400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-2800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-3800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-1200</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-600</v>
       </c>
       <c r="U81" s="3">
         <v>-200</v>
       </c>
       <c r="V81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="W81" s="3">
         <v>-200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>300</v>
       </c>
-      <c r="Y81" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,55 +6604,57 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>100</v>
+      </c>
+      <c r="F83" s="3">
         <v>600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
         <v>400</v>
       </c>
-      <c r="I83" s="3">
-        <v>100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>100</v>
-      </c>
       <c r="K83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L83" s="3">
+        <v>100</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
         <v>400</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3">
-        <v>100</v>
-      </c>
       <c r="O83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P83" s="3">
         <v>100</v>
       </c>
       <c r="Q83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -6292,8 +6689,14 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6778,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6867,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6956,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +7045,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,64 +7134,70 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-3600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-3700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-2200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-3100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-2900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-3000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-2000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-2000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-300</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-200</v>
-      </c>
-      <c r="U89" s="3">
-        <v>0</v>
       </c>
       <c r="V89" s="3">
         <v>-200</v>
@@ -6773,25 +7206,31 @@
         <v>0</v>
       </c>
       <c r="X89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
         <v>200</v>
       </c>
-      <c r="Y89" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
       <c r="AA89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-100</v>
       </c>
-      <c r="AC89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,8 +7260,10 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6830,71 +7271,71 @@
         <v>-200</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
         <v>-200</v>
       </c>
       <c r="G91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J91" s="3">
         <v>-800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-8400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>4</v>
       </c>
@@ -6904,8 +7345,14 @@
       <c r="AC91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7434,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,62 +7523,68 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-200</v>
+        <v>-500</v>
       </c>
       <c r="E94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F94" s="3">
         <v>-200</v>
       </c>
       <c r="G94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J94" s="3">
         <v>-800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1500</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-900</v>
       </c>
       <c r="L94" s="3">
         <v>-1200</v>
       </c>
       <c r="M94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="N94" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="O94" s="3">
         <v>-8400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
@@ -7133,28 +7592,34 @@
         <v>0</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC94" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7649,10 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7210,11 +7677,11 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7267,8 +7734,14 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7823,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7912,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,91 +8001,103 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>100</v>
+        <v>4500</v>
       </c>
       <c r="E100" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F100" s="3">
+        <v>100</v>
+      </c>
+      <c r="G100" s="3">
         <v>3600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>3200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>4400</v>
       </c>
-      <c r="H100" s="3">
-        <v>100</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>5400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
-        <v>100</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
+        <v>100</v>
+      </c>
+      <c r="R100" s="3">
         <v>20200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>3600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>8800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>1000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>600</v>
       </c>
-      <c r="U100" s="3">
-        <v>100</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
+        <v>100</v>
+      </c>
+      <c r="X100" s="3">
         <v>200</v>
       </c>
-      <c r="W100" s="3">
-        <v>100</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
       <c r="AA100" s="3">
-        <v>100</v>
-      </c>
-      <c r="AB100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC100" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7625,11 +8122,11 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7658,14 +8155,14 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>4</v>
+      <c r="V101" s="3">
+        <v>0</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
+      <c r="X101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y101" s="3">
         <v>0</v>
@@ -7674,76 +8171,82 @@
         <v>0</v>
       </c>
       <c r="AA101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB101" s="3">
         <v>0</v>
       </c>
       <c r="AC101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-2900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-4600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-4100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-2700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-2500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-6100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-2800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-2400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>18700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>3000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>8200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>400</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
       <c r="W102" s="3">
         <v>0</v>
       </c>
@@ -7751,18 +8254,24 @@
         <v>0</v>
       </c>
       <c r="Y102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z102" s="3">
         <v>0</v>
       </c>
       <c r="AA102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-100</v>
       </c>
-      <c r="AB102" s="3">
-        <v>100</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WKSP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WKSP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
   <si>
     <t>WKSP</t>
   </si>
@@ -656,166 +656,170 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E8" s="3">
         <v>2200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>200</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
       <c r="M8" s="3">
         <v>0</v>
       </c>
@@ -832,16 +836,16 @@
         <v>0</v>
       </c>
       <c r="R8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3">
+        <v>100</v>
+      </c>
+      <c r="T8" s="3">
         <v>200</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
       <c r="U8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V8" s="3">
         <v>100</v>
@@ -850,61 +854,64 @@
         <v>100</v>
       </c>
       <c r="X8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
         <v>1900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>200</v>
       </c>
-      <c r="AD8" s="3">
-        <v>0</v>
-      </c>
       <c r="AE8" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>200</v>
       </c>
-      <c r="L9" s="3">
-        <v>0</v>
-      </c>
       <c r="M9" s="3">
         <v>0</v>
       </c>
@@ -918,7 +925,7 @@
         <v>0</v>
       </c>
       <c r="Q9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R9" s="3">
         <v>100</v>
@@ -939,22 +946,22 @@
         <v>100</v>
       </c>
       <c r="X9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="3">
         <v>1700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>700</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>400</v>
       </c>
       <c r="AB9" s="3">
         <v>400</v>
       </c>
       <c r="AC9" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="AD9" s="3">
         <v>100</v>
@@ -962,34 +969,37 @@
       <c r="AE9" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E10" s="3">
         <v>400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>300</v>
       </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
       <c r="I10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3">
         <v>100</v>
       </c>
       <c r="K10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10" s="3">
         <v>0</v>
@@ -1007,20 +1017,20 @@
         <v>0</v>
       </c>
       <c r="Q10" s="3">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3">
         <v>-100</v>
       </c>
-      <c r="R10" s="3">
-        <v>0</v>
-      </c>
       <c r="S10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T10" s="3">
+        <v>100</v>
+      </c>
+      <c r="U10" s="3">
         <v>-100</v>
       </c>
-      <c r="U10" s="3">
-        <v>0</v>
-      </c>
       <c r="V10" s="3">
         <v>0</v>
       </c>
@@ -1031,28 +1041,31 @@
         <v>0</v>
       </c>
       <c r="Y10" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="3">
         <v>200</v>
       </c>
       <c r="AA10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC10" s="3">
         <v>200</v>
       </c>
-      <c r="AC10" s="3">
-        <v>100</v>
-      </c>
       <c r="AD10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE10" s="3">
         <v>-100</v>
       </c>
-      <c r="AE10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,32 +1097,33 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>300</v>
+      </c>
+      <c r="E12" s="3">
         <v>400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2300</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>4</v>
+      <c r="H12" s="3">
+        <v>1000</v>
       </c>
       <c r="I12" s="3">
+        <v>400</v>
+      </c>
+      <c r="J12" s="3">
         <v>1700</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1282,24 +1302,24 @@
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-300</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
@@ -1319,25 +1339,25 @@
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-200</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>4</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y14" s="3">
-        <v>-300</v>
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z14" s="3">
         <v>-300</v>
       </c>
       <c r="AA14" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1348,11 +1368,14 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1360,32 +1383,32 @@
         <v>400</v>
       </c>
       <c r="E15" s="3">
+        <v>400</v>
+      </c>
+      <c r="F15" s="3">
         <v>700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>400</v>
       </c>
-      <c r="I15" s="3">
-        <v>100</v>
-      </c>
       <c r="J15" s="3">
+        <v>100</v>
+      </c>
+      <c r="K15" s="3">
         <v>600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>200</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E17" s="3">
         <v>6500</v>
-      </c>
-      <c r="E17" s="3">
-        <v>7000</v>
       </c>
       <c r="F17" s="3">
         <v>7000</v>
       </c>
       <c r="G17" s="3">
+        <v>7000</v>
+      </c>
+      <c r="H17" s="3">
         <v>5800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4200</v>
-      </c>
-      <c r="I17" s="3">
-        <v>4400</v>
       </c>
       <c r="J17" s="3">
         <v>4400</v>
       </c>
       <c r="K17" s="3">
+        <v>4400</v>
+      </c>
+      <c r="L17" s="3">
         <v>3900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2100</v>
-      </c>
-      <c r="S17" s="3">
-        <v>1000</v>
       </c>
       <c r="T17" s="3">
         <v>1000</v>
       </c>
       <c r="U17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V17" s="3">
         <v>300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>500</v>
-      </c>
-      <c r="W17" s="3">
-        <v>200</v>
       </c>
       <c r="X17" s="3">
         <v>200</v>
       </c>
       <c r="Y17" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z17" s="3">
         <v>2200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4000</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-3900</v>
       </c>
       <c r="G18" s="3">
         <v>-3900</v>
       </c>
       <c r="H18" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="I18" s="3">
         <v>-3600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3700</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-3500</v>
       </c>
       <c r="M18" s="3">
         <v>-3500</v>
       </c>
       <c r="N18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="O18" s="3">
         <v>-3000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>300</v>
       </c>
-      <c r="AA18" s="3">
-        <v>0</v>
-      </c>
       <c r="AB18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-400</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>-300</v>
       </c>
       <c r="AE18" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1714,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1690,43 +1724,43 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
         <v>200</v>
       </c>
       <c r="O20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -1768,104 +1802,110 @@
         <v>0</v>
       </c>
       <c r="AE20" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-3400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-3300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-3400</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-3300</v>
       </c>
       <c r="M21" s="3">
         <v>-3300</v>
       </c>
       <c r="N21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="O21" s="3">
         <v>-2400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-400</v>
-      </c>
-      <c r="W21" s="3">
-        <v>-100</v>
       </c>
       <c r="X21" s="3">
         <v>-100</v>
       </c>
       <c r="Y21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>300</v>
       </c>
-      <c r="AA21" s="3">
-        <v>0</v>
-      </c>
       <c r="AB21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-500</v>
-      </c>
-      <c r="AD21" s="3">
-        <v>-300</v>
       </c>
       <c r="AE21" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
         <v>200</v>
@@ -1874,7 +1914,7 @@
         <v>200</v>
       </c>
       <c r="G22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H22" s="3">
         <v>100</v>
@@ -1886,7 +1926,7 @@
         <v>100</v>
       </c>
       <c r="K22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L22" s="3">
         <v>200</v>
@@ -1895,14 +1935,14 @@
         <v>200</v>
       </c>
       <c r="N22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O22" s="3">
+        <v>100</v>
+      </c>
+      <c r="P22" s="3">
         <v>200</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
@@ -1913,25 +1953,25 @@
         <v>0</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>200</v>
       </c>
-      <c r="U22" s="3">
-        <v>100</v>
-      </c>
       <c r="V22" s="3">
+        <v>100</v>
+      </c>
+      <c r="W22" s="3">
         <v>200</v>
       </c>
-      <c r="W22" s="3">
-        <v>100</v>
-      </c>
       <c r="X22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
@@ -1948,97 +1988,103 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4000</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-3700</v>
       </c>
       <c r="I23" s="3">
         <v>-3700</v>
       </c>
       <c r="J23" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="K23" s="3">
         <v>-3900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3800</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-3500</v>
       </c>
       <c r="M23" s="3">
         <v>-3500</v>
       </c>
       <c r="N23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="O23" s="3">
         <v>-2900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-600</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-200</v>
       </c>
       <c r="X23" s="3">
         <v>-200</v>
       </c>
       <c r="Y23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z23" s="3">
         <v>-400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>300</v>
       </c>
-      <c r="AA23" s="3">
-        <v>0</v>
-      </c>
       <c r="AB23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="3">
         <v>-100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-500</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>-300</v>
       </c>
       <c r="AE23" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2069,8 +2115,8 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -2126,8 +2172,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4000</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-3700</v>
       </c>
       <c r="I26" s="3">
         <v>-3700</v>
       </c>
       <c r="J26" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="K26" s="3">
         <v>-3900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3800</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-3500</v>
       </c>
       <c r="M26" s="3">
         <v>-3500</v>
       </c>
       <c r="N26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="O26" s="3">
         <v>-2900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-600</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-200</v>
       </c>
       <c r="X26" s="3">
         <v>-200</v>
       </c>
       <c r="Y26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z26" s="3">
         <v>-400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>300</v>
       </c>
-      <c r="AA26" s="3">
-        <v>0</v>
-      </c>
       <c r="AB26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-500</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>-300</v>
       </c>
       <c r="AE26" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4000</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-3700</v>
       </c>
       <c r="I27" s="3">
         <v>-3700</v>
       </c>
       <c r="J27" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="K27" s="3">
         <v>-3900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3800</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-3500</v>
       </c>
       <c r="M27" s="3">
         <v>-3500</v>
       </c>
       <c r="N27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="O27" s="3">
         <v>-2900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-600</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-200</v>
       </c>
       <c r="X27" s="3">
         <v>-200</v>
       </c>
       <c r="Y27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z27" s="3">
         <v>-400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>300</v>
       </c>
-      <c r="AA27" s="3">
-        <v>0</v>
-      </c>
       <c r="AB27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-500</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>-300</v>
       </c>
       <c r="AE27" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2816,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2758,43 +2828,43 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3">
         <v>-200</v>
       </c>
       <c r="O32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -2836,99 +2906,105 @@
         <v>0</v>
       </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4000</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-3700</v>
       </c>
       <c r="I33" s="3">
         <v>-3700</v>
       </c>
       <c r="J33" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="K33" s="3">
         <v>-3900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3800</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-3500</v>
       </c>
       <c r="M33" s="3">
         <v>-3500</v>
       </c>
       <c r="N33" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="O33" s="3">
         <v>-2900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-600</v>
-      </c>
-      <c r="W33" s="3">
-        <v>-200</v>
       </c>
       <c r="X33" s="3">
         <v>-200</v>
       </c>
       <c r="Y33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z33" s="3">
         <v>-400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>300</v>
       </c>
-      <c r="AA33" s="3">
-        <v>0</v>
-      </c>
       <c r="AB33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-500</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>-300</v>
       </c>
       <c r="AE33" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4000</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-3700</v>
       </c>
       <c r="I35" s="3">
         <v>-3700</v>
       </c>
       <c r="J35" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="K35" s="3">
         <v>-3900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3800</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-3500</v>
       </c>
       <c r="M35" s="3">
         <v>-3500</v>
       </c>
       <c r="N35" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="O35" s="3">
         <v>-2900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-600</v>
-      </c>
-      <c r="W35" s="3">
-        <v>-200</v>
       </c>
       <c r="X35" s="3">
         <v>-200</v>
       </c>
       <c r="Y35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z35" s="3">
         <v>-400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>300</v>
       </c>
-      <c r="AA35" s="3">
-        <v>0</v>
-      </c>
       <c r="AB35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-500</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>-300</v>
       </c>
       <c r="AE35" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,71 +3351,72 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E41" s="3">
         <v>5100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>10500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>14600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>16700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>19100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>25800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>28600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>29000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>12300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>500</v>
       </c>
-      <c r="W41" s="3">
-        <v>0</v>
-      </c>
       <c r="X41" s="3">
         <v>0</v>
       </c>
@@ -3337,58 +3424,61 @@
         <v>0</v>
       </c>
       <c r="Z41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="3">
         <v>200</v>
       </c>
-      <c r="AA41" s="3">
-        <v>100</v>
-      </c>
       <c r="AB41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC41" s="3">
         <v>0</v>
       </c>
       <c r="AD41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="3">
         <v>200</v>
       </c>
-      <c r="AE41" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E42" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>100</v>
+      </c>
+      <c r="I42" s="3">
         <v>300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1500</v>
-      </c>
-      <c r="J42" s="3">
-        <v>700</v>
       </c>
       <c r="K42" s="3">
         <v>700</v>
       </c>
       <c r="L42" s="3">
+        <v>700</v>
+      </c>
+      <c r="M42" s="3">
         <v>1500</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -3443,40 +3533,43 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>500</v>
+      </c>
+      <c r="E43" s="3">
         <v>300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>400</v>
-      </c>
-      <c r="M43" s="3">
-        <v>300</v>
       </c>
       <c r="N43" s="3">
         <v>300</v>
@@ -3485,25 +3578,25 @@
         <v>300</v>
       </c>
       <c r="P43" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Q43" s="3">
+        <v>100</v>
+      </c>
+      <c r="R43" s="3">
         <v>200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>200</v>
       </c>
-      <c r="T43" s="3">
-        <v>100</v>
-      </c>
       <c r="U43" s="3">
+        <v>100</v>
+      </c>
+      <c r="V43" s="3">
         <v>300</v>
-      </c>
-      <c r="V43" s="3">
-        <v>200</v>
       </c>
       <c r="W43" s="3">
         <v>200</v>
@@ -3512,76 +3605,79 @@
         <v>200</v>
       </c>
       <c r="Y43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z43" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA43" s="3">
         <v>200</v>
       </c>
-      <c r="AA43" s="3">
-        <v>100</v>
-      </c>
       <c r="AB43" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC43" s="3">
         <v>400</v>
       </c>
-      <c r="AC43" s="3">
-        <v>100</v>
-      </c>
       <c r="AD43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE43" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E44" s="3">
         <v>5700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6500</v>
-      </c>
-      <c r="I44" s="3">
-        <v>3600</v>
       </c>
       <c r="J44" s="3">
         <v>3600</v>
       </c>
       <c r="K44" s="3">
+        <v>3600</v>
+      </c>
+      <c r="L44" s="3">
         <v>2900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1600</v>
-      </c>
-      <c r="M44" s="3">
-        <v>1300</v>
       </c>
       <c r="N44" s="3">
         <v>1300</v>
       </c>
       <c r="O44" s="3">
+        <v>1300</v>
+      </c>
+      <c r="P44" s="3">
         <v>1100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>500</v>
       </c>
-      <c r="R44" s="3">
-        <v>100</v>
-      </c>
       <c r="S44" s="3">
         <v>100</v>
       </c>
@@ -3589,10 +3685,10 @@
         <v>100</v>
       </c>
       <c r="U44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W44" s="3">
         <v>100</v>
@@ -3604,25 +3700,28 @@
         <v>100</v>
       </c>
       <c r="Z44" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA44" s="3">
         <v>200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>300</v>
       </c>
-      <c r="AD44" s="3">
-        <v>100</v>
-      </c>
       <c r="AE44" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3653,47 +3752,47 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>2000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="V45" s="3">
-        <v>100</v>
-      </c>
       <c r="W45" s="3">
+        <v>100</v>
+      </c>
+      <c r="X45" s="3">
         <v>300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>200</v>
       </c>
-      <c r="Y45" s="3">
-        <v>100</v>
-      </c>
       <c r="Z45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA45" s="3">
         <v>0</v>
@@ -3702,90 +3801,93 @@
         <v>0</v>
       </c>
       <c r="AC45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE45" s="3">
         <v>400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E46" s="3">
         <v>11500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8900</v>
-      </c>
-      <c r="G46" s="3">
-        <v>10700</v>
       </c>
       <c r="H46" s="3">
         <v>10700</v>
       </c>
       <c r="I46" s="3">
+        <v>10700</v>
+      </c>
+      <c r="J46" s="3">
         <v>9100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>18300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>22100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>25700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>30800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>34000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>36800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>13100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>900</v>
-      </c>
-      <c r="W46" s="3">
-        <v>500</v>
       </c>
       <c r="X46" s="3">
         <v>500</v>
       </c>
       <c r="Y46" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z46" s="3">
         <v>300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>700</v>
-      </c>
-      <c r="AA46" s="3">
-        <v>500</v>
       </c>
       <c r="AB46" s="3">
         <v>500</v>
@@ -3794,13 +3896,16 @@
         <v>500</v>
       </c>
       <c r="AD46" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE46" s="3">
         <v>700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3832,7 +3937,7 @@
         <v>100</v>
       </c>
       <c r="M47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3873,8 +3978,8 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>4</v>
+      <c r="AA47" s="3">
+        <v>0</v>
       </c>
       <c r="AB47" s="3" t="s">
         <v>4</v>
@@ -3888,65 +3993,68 @@
       <c r="AE47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E48" s="3">
         <v>14000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>15000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>15100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>200</v>
       </c>
-      <c r="U48" s="3">
-        <v>100</v>
-      </c>
       <c r="V48" s="3">
         <v>100</v>
       </c>
@@ -3957,13 +4065,13 @@
         <v>100</v>
       </c>
       <c r="Y48" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z48" s="3">
         <v>200</v>
       </c>
-      <c r="Z48" s="3">
-        <v>100</v>
-      </c>
       <c r="AA48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB48" s="3">
         <v>0</v>
@@ -3977,19 +4085,22 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1000</v>
-      </c>
-      <c r="F49" s="3">
-        <v>1300</v>
       </c>
       <c r="G49" s="3">
         <v>1300</v>
@@ -4013,26 +4124,26 @@
         <v>1300</v>
       </c>
       <c r="N49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O49" s="3">
         <v>1000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>300</v>
       </c>
-      <c r="T49" s="3">
-        <v>100</v>
-      </c>
       <c r="U49" s="3">
         <v>100</v>
       </c>
@@ -4049,7 +4160,7 @@
         <v>100</v>
       </c>
       <c r="Z49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA49" s="3">
         <v>0</v>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,8 +4361,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4255,8 +4375,8 @@
       <c r="E52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
@@ -4264,21 +4384,21 @@
       <c r="H52" s="3">
         <v>0</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
       </c>
       <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>600</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
@@ -4312,8 +4432,8 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>4</v>
+      <c r="Y52" s="3">
+        <v>0</v>
       </c>
       <c r="Z52" s="3" t="s">
         <v>4</v>
@@ -4324,17 +4444,20 @@
       <c r="AB52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC52" s="3">
-        <v>0</v>
+      <c r="AC52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD52" s="3">
         <v>0</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,82 +4545,85 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E54" s="3">
         <v>26700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>25700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>24900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>26000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>24600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>30100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>32800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>35700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>38200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>34000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>36300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>38600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>14400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1100</v>
-      </c>
-      <c r="W54" s="3">
-        <v>700</v>
       </c>
       <c r="X54" s="3">
         <v>700</v>
       </c>
       <c r="Y54" s="3">
+        <v>700</v>
+      </c>
+      <c r="Z54" s="3">
         <v>500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>800</v>
-      </c>
-      <c r="AA54" s="3">
-        <v>600</v>
       </c>
       <c r="AB54" s="3">
         <v>600</v>
@@ -4506,13 +4632,16 @@
         <v>600</v>
       </c>
       <c r="AD54" s="3">
+        <v>600</v>
+      </c>
+      <c r="AE54" s="3">
         <v>700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,67 +4707,68 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1200</v>
-      </c>
-      <c r="L57" s="3">
-        <v>2000</v>
       </c>
       <c r="M57" s="3">
         <v>2000</v>
       </c>
       <c r="N57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="O57" s="3">
         <v>1800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>900</v>
-      </c>
-      <c r="T57" s="3">
-        <v>1000</v>
       </c>
       <c r="U57" s="3">
         <v>1000</v>
       </c>
       <c r="V57" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="W57" s="3">
         <v>900</v>
@@ -4646,45 +4777,48 @@
         <v>900</v>
       </c>
       <c r="Y57" s="3">
+        <v>900</v>
+      </c>
+      <c r="Z57" s="3">
         <v>1000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>900</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>600</v>
       </c>
       <c r="AB57" s="3">
         <v>600</v>
       </c>
       <c r="AC57" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD57" s="3">
         <v>400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E58" s="3">
         <v>500</v>
       </c>
       <c r="F58" s="3">
+        <v>500</v>
+      </c>
+      <c r="G58" s="3">
         <v>400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>200</v>
-      </c>
-      <c r="H58" s="3">
-        <v>5600</v>
       </c>
       <c r="I58" s="3">
         <v>5600</v>
@@ -4693,16 +4827,16 @@
         <v>5600</v>
       </c>
       <c r="K58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="L58" s="3">
         <v>5700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>400</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="O58" s="3">
         <v>300</v>
@@ -4723,19 +4857,19 @@
         <v>300</v>
       </c>
       <c r="U58" s="3">
+        <v>300</v>
+      </c>
+      <c r="V58" s="3">
         <v>700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>400</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>300</v>
       </c>
       <c r="Z58" s="3">
         <v>300</v>
@@ -4755,8 +4889,11 @@
       <c r="AE58" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4787,8 +4924,8 @@
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M59" s="3">
-        <v>400</v>
+      <c r="M59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N59" s="3">
         <v>400</v>
@@ -4797,10 +4934,10 @@
         <v>400</v>
       </c>
       <c r="P59" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q59" s="3">
         <v>200</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>300</v>
       </c>
       <c r="R59" s="3">
         <v>300</v>
@@ -4809,164 +4946,170 @@
         <v>300</v>
       </c>
       <c r="T59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="U59" s="3">
         <v>100</v>
       </c>
       <c r="V59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W59" s="3">
         <v>0</v>
       </c>
       <c r="X59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y59" s="3">
         <v>100</v>
       </c>
       <c r="Z59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA59" s="3">
         <v>0</v>
       </c>
       <c r="AB59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC59" s="3">
         <v>100</v>
       </c>
       <c r="AD59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E60" s="3">
         <v>3500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2400</v>
-      </c>
-      <c r="M60" s="3">
-        <v>2500</v>
       </c>
       <c r="N60" s="3">
         <v>2500</v>
       </c>
       <c r="O60" s="3">
+        <v>2500</v>
+      </c>
+      <c r="P60" s="3">
         <v>2400</v>
-      </c>
-      <c r="P60" s="3">
-        <v>1800</v>
       </c>
       <c r="Q60" s="3">
         <v>1800</v>
       </c>
       <c r="R60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="S60" s="3">
         <v>1700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1200</v>
-      </c>
-      <c r="AA60" s="3">
-        <v>900</v>
       </c>
       <c r="AB60" s="3">
         <v>900</v>
       </c>
       <c r="AC60" s="3">
+        <v>900</v>
+      </c>
+      <c r="AD60" s="3">
         <v>800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E61" s="3">
         <v>3000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>500</v>
-      </c>
-      <c r="I61" s="3">
-        <v>600</v>
       </c>
       <c r="J61" s="3">
         <v>600</v>
       </c>
       <c r="K61" s="3">
+        <v>600</v>
+      </c>
+      <c r="L61" s="3">
         <v>700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6100</v>
-      </c>
-      <c r="M61" s="3">
-        <v>5300</v>
       </c>
       <c r="N61" s="3">
         <v>5300</v>
@@ -4975,7 +5118,7 @@
         <v>5300</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
@@ -5022,8 +5165,11 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5054,29 +5200,29 @@
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
         <v>900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1100</v>
-      </c>
-      <c r="P62" s="3">
-        <v>300</v>
       </c>
       <c r="Q62" s="3">
         <v>300</v>
       </c>
       <c r="R62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="S62" s="3">
         <v>400</v>
       </c>
       <c r="T62" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
@@ -5096,8 +5242,8 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>4</v>
+      <c r="AA62" s="3">
+        <v>0</v>
       </c>
       <c r="AB62" s="3" t="s">
         <v>4</v>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,49 +5533,52 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E66" s="3">
         <v>6500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8600</v>
-      </c>
-      <c r="N66" s="3">
-        <v>8800</v>
       </c>
       <c r="O66" s="3">
         <v>8800</v>
       </c>
       <c r="P66" s="3">
-        <v>2100</v>
+        <v>8800</v>
       </c>
       <c r="Q66" s="3">
         <v>2100</v>
@@ -5429,46 +5587,49 @@
         <v>2100</v>
       </c>
       <c r="S66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="T66" s="3">
         <v>1900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1500</v>
-      </c>
-      <c r="X66" s="3">
-        <v>1400</v>
       </c>
       <c r="Y66" s="3">
         <v>1400</v>
       </c>
       <c r="Z66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AA66" s="3">
         <v>1300</v>
-      </c>
-      <c r="AA66" s="3">
-        <v>900</v>
       </c>
       <c r="AB66" s="3">
         <v>900</v>
       </c>
       <c r="AC66" s="3">
+        <v>900</v>
+      </c>
+      <c r="AD66" s="3">
         <v>800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6027,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-68900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-64500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-60200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-56000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-52000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-48300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-44700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-40700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-36900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-33400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-29900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-27000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-23700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-20800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-17100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-14900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-14100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-12900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-12600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-12000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-10800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-10200</v>
-      </c>
-      <c r="AA72" s="3">
-        <v>-10500</v>
       </c>
       <c r="AB72" s="3">
         <v>-10500</v>
       </c>
       <c r="AC72" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="AD72" s="3">
         <v>-10400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-9900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E76" s="3">
         <v>20100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>17400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>19100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>24100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>26900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>29400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>31900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>34200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>36500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-400</v>
-      </c>
-      <c r="AA76" s="3">
-        <v>-300</v>
       </c>
       <c r="AB76" s="3">
         <v>-300</v>
       </c>
       <c r="AC76" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AD76" s="3">
         <v>-200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4000</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-3700</v>
       </c>
       <c r="I81" s="3">
         <v>-3700</v>
       </c>
       <c r="J81" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="K81" s="3">
         <v>-3900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3800</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-3500</v>
       </c>
       <c r="M81" s="3">
         <v>-3500</v>
       </c>
       <c r="N81" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="O81" s="3">
         <v>-2900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-600</v>
-      </c>
-      <c r="W81" s="3">
-        <v>-200</v>
       </c>
       <c r="X81" s="3">
         <v>-200</v>
       </c>
       <c r="Y81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z81" s="3">
         <v>-400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>300</v>
       </c>
-      <c r="AA81" s="3">
-        <v>0</v>
-      </c>
       <c r="AB81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-500</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>-300</v>
       </c>
       <c r="AE81" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,49 +6804,50 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>200</v>
+      </c>
+      <c r="E83" s="3">
         <v>400</v>
       </c>
-      <c r="E83" s="3">
-        <v>100</v>
-      </c>
       <c r="F83" s="3">
+        <v>100</v>
+      </c>
+      <c r="G83" s="3">
         <v>600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
       <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
         <v>400</v>
       </c>
-      <c r="K83" s="3">
-        <v>100</v>
-      </c>
       <c r="L83" s="3">
         <v>100</v>
       </c>
       <c r="M83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
         <v>400</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
       <c r="P83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q83" s="3">
         <v>100</v>
@@ -6657,7 +6856,7 @@
         <v>100</v>
       </c>
       <c r="S83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3000</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-2000</v>
       </c>
       <c r="Q89" s="3">
         <v>-2000</v>
       </c>
       <c r="R89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="S89" s="3">
         <v>-1000</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-500</v>
       </c>
       <c r="T89" s="3">
         <v>-500</v>
       </c>
       <c r="U89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="V89" s="3">
         <v>-300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-200</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
       <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-200</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
       <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
         <v>200</v>
       </c>
-      <c r="AA89" s="3">
-        <v>100</v>
-      </c>
       <c r="AB89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-100</v>
       </c>
-      <c r="AE89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,67 +7482,68 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-200</v>
       </c>
       <c r="I91" s="3">
         <v>-200</v>
       </c>
       <c r="J91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>4</v>
@@ -7330,14 +7551,14 @@
       <c r="X91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y91" s="3">
-        <v>-100</v>
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>4</v>
+      <c r="AA91" s="3">
+        <v>-100</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>4</v>
@@ -7351,8 +7572,11 @@
       <c r="AE91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,65 +7756,68 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-500</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-100</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-200</v>
       </c>
       <c r="I94" s="3">
         <v>-200</v>
       </c>
       <c r="J94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
@@ -7598,28 +7828,31 @@
         <v>0</v>
       </c>
       <c r="Y94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>4</v>
+      <c r="AA94" s="3">
+        <v>-100</v>
       </c>
       <c r="AB94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
+      <c r="AC94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7683,8 +7917,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,79 +8250,82 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E100" s="3">
         <v>4500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5200</v>
       </c>
-      <c r="F100" s="3">
-        <v>100</v>
-      </c>
       <c r="G100" s="3">
+        <v>100</v>
+      </c>
+      <c r="H100" s="3">
         <v>3600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4400</v>
       </c>
-      <c r="J100" s="3">
-        <v>100</v>
-      </c>
       <c r="K100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>5400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
-        <v>100</v>
-      </c>
       <c r="R100" s="3">
+        <v>100</v>
+      </c>
+      <c r="S100" s="3">
         <v>20200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>3600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>8800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>600</v>
       </c>
-      <c r="W100" s="3">
-        <v>100</v>
-      </c>
       <c r="X100" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y100" s="3">
         <v>200</v>
       </c>
-      <c r="Y100" s="3">
-        <v>100</v>
-      </c>
       <c r="Z100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA100" s="3">
         <v>0</v>
@@ -8088,16 +8334,19 @@
         <v>0</v>
       </c>
       <c r="AC100" s="3">
-        <v>100</v>
-      </c>
-      <c r="AD100" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
+        <v>100</v>
       </c>
       <c r="AE100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8128,8 +8377,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -8161,11 +8410,11 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>0</v>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
@@ -8177,79 +8426,82 @@
         <v>0</v>
       </c>
       <c r="AC101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>18700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>8200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>400</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
       <c r="X102" s="3">
         <v>0</v>
       </c>
@@ -8260,18 +8512,21 @@
         <v>0</v>
       </c>
       <c r="AA102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-100</v>
       </c>
-      <c r="AD102" s="3">
-        <v>100</v>
-      </c>
       <c r="AE102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WKSP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WKSP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="92">
   <si>
     <t>WKSP</t>
   </si>
@@ -656,183 +656,190 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F8" s="3">
         <v>5000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>4100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>2200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>2900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>3100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1900</v>
-      </c>
-      <c r="J8" s="3">
-        <v>500</v>
-      </c>
-      <c r="K8" s="3">
-        <v>800</v>
       </c>
       <c r="L8" s="3">
         <v>500</v>
       </c>
       <c r="M8" s="3">
+        <v>800</v>
+      </c>
+      <c r="N8" s="3">
+        <v>500</v>
+      </c>
+      <c r="O8" s="3">
         <v>200</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
       <c r="P8" s="3">
         <v>0</v>
       </c>
@@ -846,88 +853,94 @@
         <v>0</v>
       </c>
       <c r="T8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
+        <v>100</v>
+      </c>
+      <c r="W8" s="3">
         <v>200</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
-      </c>
-      <c r="W8" s="3">
-        <v>100</v>
-      </c>
       <c r="X8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3">
         <v>100</v>
       </c>
       <c r="Z8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
         <v>1900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>200</v>
       </c>
-      <c r="AF8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F9" s="3">
         <v>3400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>3000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>2600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>2900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>200</v>
       </c>
-      <c r="N9" s="3">
-        <v>0</v>
-      </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
       <c r="P9" s="3">
         <v>0</v>
       </c>
@@ -938,10 +951,10 @@
         <v>0</v>
       </c>
       <c r="S9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U9" s="3">
         <v>100</v>
@@ -959,66 +972,72 @@
         <v>100</v>
       </c>
       <c r="Z9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA9" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="3">
         <v>1700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>400</v>
       </c>
-      <c r="AE9" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF9" s="3">
-        <v>100</v>
-      </c>
       <c r="AG9" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI9" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F10" s="3">
         <v>1600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>400</v>
-      </c>
-      <c r="G10" s="3">
-        <v>300</v>
-      </c>
-      <c r="H10" s="3">
-        <v>200</v>
       </c>
       <c r="I10" s="3">
         <v>300</v>
       </c>
       <c r="J10" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K10" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10" s="3">
         <v>0</v>
@@ -1033,23 +1052,23 @@
         <v>0</v>
       </c>
       <c r="S10" s="3">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3">
         <v>-100</v>
       </c>
-      <c r="T10" s="3">
-        <v>0</v>
-      </c>
-      <c r="U10" s="3">
-        <v>100</v>
-      </c>
       <c r="V10" s="3">
+        <v>0</v>
+      </c>
+      <c r="W10" s="3">
+        <v>100</v>
+      </c>
+      <c r="X10" s="3">
         <v>-100</v>
       </c>
-      <c r="W10" s="3">
-        <v>0</v>
-      </c>
-      <c r="X10" s="3">
-        <v>0</v>
-      </c>
       <c r="Y10" s="3">
         <v>0</v>
       </c>
@@ -1057,13 +1076,13 @@
         <v>0</v>
       </c>
       <c r="AA10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="3">
         <v>200</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>200</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>100</v>
       </c>
       <c r="AD10" s="3">
         <v>200</v>
@@ -1072,13 +1091,19 @@
         <v>100</v>
       </c>
       <c r="AF10" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH10" s="3">
         <v>-100</v>
       </c>
-      <c r="AG10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,41 +1137,43 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>200</v>
+      </c>
+      <c r="E12" s="3">
+        <v>600</v>
+      </c>
+      <c r="F12" s="3">
         <v>300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>300</v>
-      </c>
-      <c r="F12" s="3">
-        <v>400</v>
-      </c>
-      <c r="G12" s="3">
-        <v>2300</v>
       </c>
       <c r="H12" s="3">
         <v>400</v>
       </c>
       <c r="I12" s="3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J12" s="3">
         <v>400</v>
       </c>
       <c r="K12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L12" s="3">
+        <v>400</v>
+      </c>
+      <c r="M12" s="3">
         <v>1700</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
@@ -1207,8 +1234,14 @@
       <c r="AG12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,8 +1335,14 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1328,27 +1367,27 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-300</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1365,82 +1404,88 @@
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-200</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC14" s="3">
         <v>-300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>-300</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>400</v>
+      </c>
+      <c r="E15" s="3">
         <v>500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
+        <v>500</v>
+      </c>
+      <c r="G15" s="3">
         <v>400</v>
-      </c>
-      <c r="F15" s="3">
-        <v>400</v>
-      </c>
-      <c r="G15" s="3">
-        <v>700</v>
       </c>
       <c r="H15" s="3">
         <v>400</v>
       </c>
       <c r="I15" s="3">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="J15" s="3">
         <v>400</v>
       </c>
       <c r="K15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L15" s="3">
+        <v>400</v>
+      </c>
+      <c r="M15" s="3">
+        <v>100</v>
+      </c>
+      <c r="N15" s="3">
         <v>600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>200</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1492,8 +1537,14 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1575,212 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>10900</v>
+      </c>
+      <c r="F17" s="3">
         <v>9800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>7700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>6500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>7000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>7000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>5800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>3900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>3500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>3000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>3300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>3700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-4800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-3600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-4300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-4000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-3900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-3900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-3600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-3500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-3900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-3700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-3500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-3500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-3300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-2800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-3700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-2000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-1000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>300</v>
       </c>
-      <c r="AC18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="3">
         <v>-100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,8 +1814,10 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1758,13 +1825,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -1773,37 +1840,37 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
-        <v>100</v>
-      </c>
-      <c r="R20" s="3">
-        <v>100</v>
-      </c>
       <c r="S20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U20" s="3">
         <v>0</v>
@@ -1842,39 +1909,45 @@
         <v>0</v>
       </c>
       <c r="AG20" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-4300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-3200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-3800</v>
       </c>
-      <c r="G21" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="J21" s="3">
         <v>-3500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-3600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-3200</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-3300</v>
       </c>
       <c r="M21" s="3">
         <v>-3400</v>
@@ -1883,64 +1956,70 @@
         <v>-3300</v>
       </c>
       <c r="O21" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="P21" s="3">
         <v>-3300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="R21" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-3200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-2700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-3800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-1900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-1000</v>
-      </c>
-      <c r="W21" s="3">
-        <v>-100</v>
-      </c>
-      <c r="X21" s="3">
-        <v>-400</v>
       </c>
       <c r="Y21" s="3">
         <v>-100</v>
       </c>
       <c r="Z21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>300</v>
       </c>
-      <c r="AC21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1951,19 +2030,19 @@
         <v>100</v>
       </c>
       <c r="F22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H22" s="3">
         <v>200</v>
       </c>
       <c r="I22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K22" s="3">
         <v>100</v>
@@ -1972,25 +2051,25 @@
         <v>100</v>
       </c>
       <c r="M22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O22" s="3">
         <v>200</v>
       </c>
       <c r="P22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q22" s="3">
         <v>200</v>
       </c>
       <c r="R22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -1999,10 +2078,10 @@
         <v>0</v>
       </c>
       <c r="V22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="W22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X22" s="3">
         <v>200</v>
@@ -2011,7 +2090,7 @@
         <v>100</v>
       </c>
       <c r="Z22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AA22" s="3">
         <v>100</v>
@@ -2020,7 +2099,7 @@
         <v>0</v>
       </c>
       <c r="AC22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
@@ -2034,103 +2113,115 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-4900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-3700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-4500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-4300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-4100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-4000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-3700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-3700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-3900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-3800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-3500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-3500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-3400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-2800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-3800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-2100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-1200</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-200</v>
-      </c>
-      <c r="X23" s="3">
-        <v>-600</v>
       </c>
       <c r="Y23" s="3">
         <v>-200</v>
       </c>
       <c r="Z23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AC23" s="3">
         <v>-400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>300</v>
       </c>
-      <c r="AC23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="3">
         <v>-100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2167,11 +2258,11 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2224,8 +2315,14 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2416,216 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-4900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-3700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-4500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-4300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-4100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-4000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-3700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-3700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-3900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-3800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-3500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-3500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-3400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-2800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-3800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-2100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-1200</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-600</v>
       </c>
       <c r="Y26" s="3">
         <v>-200</v>
       </c>
       <c r="Z26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>300</v>
       </c>
-      <c r="AC26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="3">
         <v>-100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-4900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-3700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-4500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-4300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-4100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-4000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-3700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-3700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-3900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-3800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-3500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-3500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-3400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-2800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-3800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-2100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-1200</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="X27" s="3">
-        <v>-600</v>
       </c>
       <c r="Y27" s="3">
         <v>-200</v>
       </c>
       <c r="Z27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>300</v>
       </c>
-      <c r="AC27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2719,14 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2699,8 +2820,14 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2921,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,8 +3022,14 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2898,189 +3037,201 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>100</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>100</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-4900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-3700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-4500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-4300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-4100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-4000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-3700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-3700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-3900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-3800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-3500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-3500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-3400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-2800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-3800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-2100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-1200</v>
-      </c>
-      <c r="W33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="X33" s="3">
-        <v>-600</v>
       </c>
       <c r="Y33" s="3">
         <v>-200</v>
       </c>
       <c r="Z33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>300</v>
       </c>
-      <c r="AC33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="3">
         <v>-100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3325,221 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-4900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-3700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-4500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-4300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-4100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-4000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-3700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-3700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-3900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-3800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-3500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-3500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-3400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-2800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-3800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-2100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-1200</v>
-      </c>
-      <c r="W35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="X35" s="3">
-        <v>-600</v>
       </c>
       <c r="Y35" s="3">
         <v>-200</v>
       </c>
       <c r="Z35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>300</v>
       </c>
-      <c r="AC35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="3">
         <v>-100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3573,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,108 +3610,116 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F41" s="3">
         <v>3800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>5100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1900</v>
-      </c>
-      <c r="I41" s="3">
-        <v>3400</v>
-      </c>
-      <c r="J41" s="3">
-        <v>3500</v>
       </c>
       <c r="K41" s="3">
         <v>3400</v>
       </c>
       <c r="L41" s="3">
+        <v>3500</v>
+      </c>
+      <c r="M41" s="3">
+        <v>3400</v>
+      </c>
+      <c r="N41" s="3">
         <v>3000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>5900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>10500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>14600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>16700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>19100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>25800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>28600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>29000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>12300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>9300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>500</v>
       </c>
-      <c r="Y41" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>0</v>
-      </c>
       <c r="AA41" s="3">
         <v>0</v>
       </c>
       <c r="AB41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="3">
         <v>200</v>
       </c>
-      <c r="AC41" s="3">
-        <v>100</v>
-      </c>
-      <c r="AD41" s="3">
-        <v>0</v>
-      </c>
       <c r="AE41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="3">
         <v>200</v>
       </c>
-      <c r="AG41" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>200</v>
@@ -3549,35 +3728,35 @@
         <v>200</v>
       </c>
       <c r="G42" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I42" s="3">
         <v>100</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>100</v>
+      </c>
+      <c r="L42" s="3">
         <v>300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>1500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>1500</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -3629,82 +3808,88 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>800</v>
+      </c>
+      <c r="F43" s="3">
         <v>700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>300</v>
-      </c>
-      <c r="K43" s="3">
-        <v>600</v>
-      </c>
-      <c r="L43" s="3">
-        <v>700</v>
       </c>
       <c r="M43" s="3">
         <v>600</v>
       </c>
       <c r="N43" s="3">
+        <v>700</v>
+      </c>
+      <c r="O43" s="3">
+        <v>600</v>
+      </c>
+      <c r="P43" s="3">
         <v>400</v>
-      </c>
-      <c r="O43" s="3">
-        <v>300</v>
-      </c>
-      <c r="P43" s="3">
-        <v>300</v>
       </c>
       <c r="Q43" s="3">
         <v>300</v>
       </c>
       <c r="R43" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="S43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="T43" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="U43" s="3">
         <v>200</v>
       </c>
       <c r="V43" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="W43" s="3">
+        <v>200</v>
+      </c>
+      <c r="X43" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y43" s="3">
         <v>300</v>
-      </c>
-      <c r="X43" s="3">
-        <v>200</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>200</v>
       </c>
       <c r="Z43" s="3">
         <v>200</v>
       </c>
       <c r="AA43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB43" s="3">
         <v>200</v>
@@ -3713,87 +3898,93 @@
         <v>100</v>
       </c>
       <c r="AD43" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE43" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF43" s="3">
         <v>400</v>
       </c>
-      <c r="AE43" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF43" s="3">
-        <v>0</v>
-      </c>
       <c r="AG43" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>9500</v>
+      </c>
+      <c r="F44" s="3">
         <v>6800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>5900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>5700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>5200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>6100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>6400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>6500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>3600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>3600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>2900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>1100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>500</v>
       </c>
-      <c r="T44" s="3">
-        <v>100</v>
-      </c>
-      <c r="U44" s="3">
-        <v>100</v>
-      </c>
       <c r="V44" s="3">
         <v>100</v>
       </c>
       <c r="W44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X44" s="3">
         <v>100</v>
       </c>
       <c r="Y44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z44" s="3">
         <v>100</v>
@@ -3802,10 +3993,10 @@
         <v>100</v>
       </c>
       <c r="AB44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC44" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AD44" s="3">
         <v>200</v>
@@ -3814,13 +4005,19 @@
         <v>300</v>
       </c>
       <c r="AF44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AG44" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3857,160 +4054,172 @@
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3">
         <v>2000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>3700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>5100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>4100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>4700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>7400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>200</v>
       </c>
-      <c r="X45" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA45" s="3">
         <v>300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>200</v>
       </c>
-      <c r="AA45" s="3">
-        <v>100</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>0</v>
-      </c>
       <c r="AC45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD45" s="3">
         <v>0</v>
       </c>
       <c r="AE45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH45" s="3">
         <v>400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>16800</v>
+      </c>
+      <c r="F46" s="3">
         <v>12400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>8500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>11500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>10500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>8900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>10700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>10700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>9100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>7900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>10500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>14700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>18300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>22100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>25700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>30800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>34000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>36800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>13100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>9800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>700</v>
-      </c>
-      <c r="AC46" s="3">
-        <v>500</v>
-      </c>
-      <c r="AD46" s="3">
-        <v>500</v>
       </c>
       <c r="AE46" s="3">
         <v>500</v>
       </c>
       <c r="AF46" s="3">
+        <v>500</v>
+      </c>
+      <c r="AG46" s="3">
+        <v>500</v>
+      </c>
+      <c r="AH46" s="3">
         <v>700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4048,10 +4257,10 @@
         <v>100</v>
       </c>
       <c r="O47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4089,11 +4298,11 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD47" s="3" t="s">
-        <v>4</v>
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="3">
+        <v>0</v>
       </c>
       <c r="AE47" s="3" t="s">
         <v>4</v>
@@ -4104,74 +4313,80 @@
       <c r="AG47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>13000</v>
+      </c>
+      <c r="F48" s="3">
         <v>13500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>13900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>14000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>14200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>14600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>15000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>15100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>15400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>15300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>15100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>13400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>13100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>12600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>11700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>1000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>200</v>
       </c>
-      <c r="W48" s="3">
-        <v>100</v>
-      </c>
-      <c r="X48" s="3">
-        <v>100</v>
-      </c>
       <c r="Y48" s="3">
         <v>100</v>
       </c>
@@ -4179,16 +4394,16 @@
         <v>100</v>
       </c>
       <c r="AA48" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB48" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC48" s="3">
         <v>200</v>
       </c>
-      <c r="AB48" s="3">
-        <v>100</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>0</v>
-      </c>
       <c r="AD48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE48" s="3">
         <v>0</v>
@@ -4199,28 +4414,34 @@
       <c r="AG48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>900</v>
+      </c>
+      <c r="F49" s="3">
         <v>1000</v>
-      </c>
-      <c r="E49" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F49" s="3">
-        <v>1100</v>
       </c>
       <c r="G49" s="3">
         <v>1000</v>
       </c>
       <c r="H49" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="I49" s="3">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="J49" s="3">
         <v>1300</v>
@@ -4241,29 +4462,29 @@
         <v>1300</v>
       </c>
       <c r="P49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="R49" s="3">
         <v>1000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>300</v>
       </c>
-      <c r="V49" s="3">
-        <v>100</v>
-      </c>
-      <c r="W49" s="3">
-        <v>100</v>
-      </c>
       <c r="X49" s="3">
         <v>100</v>
       </c>
@@ -4277,10 +4498,10 @@
         <v>100</v>
       </c>
       <c r="AB49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD49" s="3">
         <v>0</v>
@@ -4294,8 +4515,14 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4616,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,8 +4717,14 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4501,33 +4740,33 @@
       <c r="G52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J52" s="3">
         <v>0</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
+      <c r="K52" s="3">
+        <v>0</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>600</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
       <c r="Q52" s="3">
         <v>0</v>
       </c>
@@ -4558,11 +4797,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB52" s="3" t="s">
-        <v>4</v>
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="3">
+        <v>0</v>
       </c>
       <c r="AC52" s="3" t="s">
         <v>4</v>
@@ -4570,17 +4809,23 @@
       <c r="AD52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4919,115 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>30700</v>
+      </c>
+      <c r="F54" s="3">
         <v>27000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>23600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>26700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>25700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>24900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>27200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>27300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>26000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>24600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>27000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>30100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>32800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>35700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>38200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>34000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>36300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>38600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>14400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>10200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>800</v>
-      </c>
-      <c r="AC54" s="3">
-        <v>600</v>
-      </c>
-      <c r="AD54" s="3">
-        <v>600</v>
       </c>
       <c r="AE54" s="3">
         <v>600</v>
       </c>
       <c r="AF54" s="3">
+        <v>600</v>
+      </c>
+      <c r="AG54" s="3">
+        <v>600</v>
+      </c>
+      <c r="AH54" s="3">
         <v>700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +5061,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,8 +5098,10 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4848,138 +5109,144 @@
         <v>2800</v>
       </c>
       <c r="E57" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F57" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G57" s="3">
         <v>2000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>2000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1000</v>
-      </c>
-      <c r="X57" s="3">
-        <v>900</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>900</v>
       </c>
       <c r="Z57" s="3">
         <v>900</v>
       </c>
       <c r="AA57" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB57" s="3">
         <v>900</v>
       </c>
       <c r="AC57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AD57" s="3">
+        <v>900</v>
+      </c>
+      <c r="AE57" s="3">
         <v>600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F58" s="3">
         <v>1900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>200</v>
-      </c>
-      <c r="J58" s="3">
-        <v>5600</v>
-      </c>
-      <c r="K58" s="3">
-        <v>5600</v>
       </c>
       <c r="L58" s="3">
         <v>5600</v>
       </c>
       <c r="M58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="N58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="O58" s="3">
         <v>5700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>400</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>300</v>
-      </c>
       <c r="Q58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="R58" s="3">
         <v>300</v>
@@ -4997,22 +5264,22 @@
         <v>300</v>
       </c>
       <c r="W58" s="3">
+        <v>300</v>
+      </c>
+      <c r="X58" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y58" s="3">
         <v>700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>400</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>300</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>300</v>
       </c>
       <c r="AC58" s="3">
         <v>300</v>
@@ -5029,8 +5296,14 @@
       <c r="AG58" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5067,210 +5340,222 @@
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O59" s="3">
-        <v>400</v>
-      </c>
-      <c r="P59" s="3">
-        <v>400</v>
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q59" s="3">
         <v>400</v>
       </c>
       <c r="R59" s="3">
+        <v>400</v>
+      </c>
+      <c r="S59" s="3">
+        <v>400</v>
+      </c>
+      <c r="T59" s="3">
         <v>200</v>
-      </c>
-      <c r="S59" s="3">
-        <v>300</v>
-      </c>
-      <c r="T59" s="3">
-        <v>300</v>
       </c>
       <c r="U59" s="3">
         <v>300</v>
       </c>
       <c r="V59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="W59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="X59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F60" s="3">
         <v>6100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>7800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>7200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>7600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>6900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>2500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>1300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>1200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>1200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F61" s="3">
         <v>1200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>3000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>5100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>5600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>5800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>6100</v>
-      </c>
-      <c r="O61" s="3">
-        <v>5300</v>
-      </c>
-      <c r="P61" s="3">
-        <v>5300</v>
       </c>
       <c r="Q61" s="3">
         <v>5300</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
@@ -5314,8 +5599,14 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5352,33 +5643,33 @@
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q62" s="3">
         <v>900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>1100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>400</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
-      </c>
-      <c r="W62" s="3">
-        <v>0</v>
-      </c>
       <c r="X62" s="3">
         <v>0</v>
       </c>
@@ -5394,11 +5685,11 @@
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD62" s="3" t="s">
-        <v>4</v>
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="3">
+        <v>0</v>
       </c>
       <c r="AE62" s="3" t="s">
         <v>4</v>
@@ -5409,8 +5700,14 @@
       <c r="AG62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5801,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5902,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +6003,115 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F66" s="3">
         <v>7300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>6300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>6500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>8300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>8600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>8000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>8400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>7800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>8200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>7600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>8500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>8600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>8800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>8800</v>
-      </c>
-      <c r="R66" s="3">
-        <v>2100</v>
-      </c>
-      <c r="S66" s="3">
-        <v>2100</v>
       </c>
       <c r="T66" s="3">
         <v>2100</v>
       </c>
       <c r="U66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="V66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="W66" s="3">
         <v>1900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>1200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +6145,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6242,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6343,14 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6444,14 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6545,115 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-89700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-83900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-77600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-72700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-68900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-64500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-60200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-56000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-52000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-48300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-44700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-40700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-36900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-33400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-29900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-27000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-23700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-20800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-17100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-14900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-14100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-12900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-12600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-10500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-10500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-10400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-9900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6747,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6848,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6949,115 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>22900</v>
+      </c>
+      <c r="F76" s="3">
         <v>19800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>17300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>20100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>17400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>16400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>19100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>18900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>18200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>16400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>19400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>21600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>24100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>26900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>29400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>31900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>34200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>36500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>12500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>8800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>-400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>-800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>-900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>-400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>-300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>-300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>-200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>-500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +7151,221 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-4900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-3700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-4500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-4300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-4100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-4000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-3700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-3700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-3900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-3800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-3500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-3500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-3400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-2800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-3800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-2100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-1200</v>
-      </c>
-      <c r="W81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="X81" s="3">
-        <v>-600</v>
       </c>
       <c r="Y81" s="3">
         <v>-200</v>
       </c>
       <c r="Z81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>300</v>
       </c>
-      <c r="AC81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="3">
         <v>-100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,67 +7399,69 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F83" s="3">
         <v>400</v>
       </c>
       <c r="G83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H83" s="3">
+        <v>400</v>
+      </c>
+      <c r="I83" s="3">
+        <v>100</v>
+      </c>
+      <c r="J83" s="3">
         <v>600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
         <v>400</v>
       </c>
-      <c r="M83" s="3">
-        <v>100</v>
-      </c>
-      <c r="N83" s="3">
-        <v>100</v>
-      </c>
       <c r="O83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
         <v>400</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3">
-        <v>100</v>
-      </c>
       <c r="S83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T83" s="3">
         <v>100</v>
       </c>
       <c r="U83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
@@ -7099,8 +7496,14 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7597,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7698,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7799,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7900,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,76 +8001,82 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-4300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-3100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-3800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-2200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-3600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-2800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-3700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-3100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-2900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-1600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-3000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-2000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-2000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-1000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-300</v>
-      </c>
-      <c r="X89" s="3">
-        <v>-200</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>0</v>
       </c>
       <c r="Z89" s="3">
         <v>-200</v>
@@ -7652,25 +8085,31 @@
         <v>0</v>
       </c>
       <c r="AB89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3">
         <v>200</v>
       </c>
-      <c r="AC89" s="3">
-        <v>100</v>
-      </c>
-      <c r="AD89" s="3">
-        <v>0</v>
-      </c>
       <c r="AE89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-100</v>
       </c>
-      <c r="AG89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,92 +8143,94 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>-200</v>
       </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-200</v>
       </c>
       <c r="K91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N91" s="3">
         <v>-800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-8400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y91" s="3" t="s">
-        <v>4</v>
+      <c r="Y91" s="3">
+        <v>0</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-100</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE91" s="3" t="s">
         <v>4</v>
       </c>
@@ -7799,8 +8240,14 @@
       <c r="AG91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8341,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,13 +8442,19 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-500</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
         <v>-100</v>
@@ -8004,59 +8463,59 @@
         <v>-500</v>
       </c>
       <c r="G94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H94" s="3">
-        <v>-200</v>
+        <v>-500</v>
       </c>
       <c r="I94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J94" s="3">
         <v>-200</v>
       </c>
       <c r="K94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N94" s="3">
         <v>-800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1500</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-900</v>
       </c>
       <c r="P94" s="3">
         <v>-1200</v>
       </c>
       <c r="Q94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="R94" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="S94" s="3">
         <v>-8400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
         <v>0</v>
       </c>
@@ -8064,28 +8523,34 @@
         <v>0</v>
       </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-100</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG94" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,13 +8584,15 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
+      <c r="D96" s="3">
+        <v>0</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>4</v>
@@ -8157,11 +8624,11 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -8214,8 +8681,14 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8782,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8883,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,103 +8984,115 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F100" s="3">
         <v>7100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>4500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>5200</v>
       </c>
-      <c r="H100" s="3">
-        <v>100</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>100</v>
+      </c>
+      <c r="K100" s="3">
         <v>3600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>3200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>4400</v>
       </c>
-      <c r="L100" s="3">
-        <v>100</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>5400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
-        <v>100</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
+        <v>100</v>
+      </c>
+      <c r="V100" s="3">
         <v>20200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>3600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>8800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>1000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>600</v>
       </c>
-      <c r="Y100" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB100" s="3">
         <v>200</v>
       </c>
-      <c r="AA100" s="3">
-        <v>100</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD100" s="3">
         <v>0</v>
       </c>
       <c r="AE100" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG100" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8632,11 +9129,11 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8665,14 +9162,14 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>4</v>
+      <c r="Z101" s="3">
+        <v>0</v>
       </c>
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
+      <c r="AB101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC101" s="3">
         <v>0</v>
@@ -8681,88 +9178,94 @@
         <v>0</v>
       </c>
       <c r="AE101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF101" s="3">
         <v>0</v>
       </c>
       <c r="AG101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F102" s="3">
         <v>2400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-3700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>3000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-2900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-4600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-4100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-2700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-6100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-2800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-2400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>18700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>3000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>8200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>400</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
       <c r="AA102" s="3">
         <v>0</v>
       </c>
@@ -8770,18 +9273,24 @@
         <v>0</v>
       </c>
       <c r="AC102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD102" s="3">
         <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>-100</v>
       </c>
-      <c r="AF102" s="3">
-        <v>100</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>
